--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_shoe.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_shoe.xlsx
@@ -1121,43 +1121,43 @@
         <v>17.827868852459</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>104.686010555719</v>
       </c>
       <c r="G2">
         <v>1.76260162601626</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.134325203252033</v>
       </c>
       <c r="I2">
         <v>0.131218980752935</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>717.7</v>
       </c>
       <c r="L2">
-        <v>853.826360235567</v>
+        <v>844.922162476195</v>
       </c>
       <c r="M2">
         <v>612.6</v>
       </c>
       <c r="N2">
-        <v>640.326360235567</v>
+        <v>639.683162476195</v>
       </c>
       <c r="O2">
         <v>108.4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>8.260999999999999</v>
       </c>
       <c r="Q2">
         <v>0.09257968560710721</v>
       </c>
       <c r="R2">
-        <v>0.0905541085023757</v>
+        <v>0.09059910850237569</v>
       </c>
       <c r="S2">
         <v>0.0612366166625341</v>
@@ -1179,13 +1179,13 @@
         <v>0.097313681250958</v>
       </c>
       <c r="X2">
-        <v>0.0905541085023757</v>
+        <v>0.0910061702044199</v>
       </c>
       <c r="Y2">
         <v>1.00409752994566</v>
       </c>
       <c r="Z2">
-        <v>0.872340875489653</v>
+        <v>0.881152399484498</v>
       </c>
       <c r="AA2">
         <v>108.4</v>
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09055410850237572</v>
+        <v>0.09059910850237572</v>
       </c>
       <c r="C2">
-        <v>853.8263602355669</v>
+        <v>844.9221624761947</v>
       </c>
       <c r="D2">
-        <v>640.3263602355669</v>
+        <v>639.6831624761946</v>
       </c>
       <c r="E2">
-        <v>-108.4</v>
+        <v>-100.139</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.261000000000001</v>
       </c>
       <c r="G2">
         <v>213.5</v>
@@ -1439,28 +1439,28 @@
         <v>43.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4155283</v>
       </c>
       <c r="N2">
-        <v>43.5</v>
+        <v>43.0844717</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>43.5</v>
+        <v>43.0844717</v>
       </c>
       <c r="Q2">
-        <v>61.5</v>
+        <v>61.0844717</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09055410850237572</v>
+        <v>0.09100617020441992</v>
       </c>
       <c r="T2">
-        <v>0.8723408754896529</v>
+        <v>0.881152399484498</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>104.6860105557191</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09059910850237572</v>
+        <v>0.09064410850237573</v>
       </c>
       <c r="C3">
-        <v>844.9221624761947</v>
+        <v>836.0192555842357</v>
       </c>
       <c r="D3">
-        <v>639.6831624761946</v>
+        <v>639.0412555842357</v>
       </c>
       <c r="E3">
-        <v>-100.139</v>
+        <v>-91.878</v>
       </c>
       <c r="F3">
-        <v>8.261000000000001</v>
+        <v>16.522</v>
       </c>
       <c r="G3">
         <v>213.5</v>
@@ -1521,28 +1521,28 @@
         <v>43.5</v>
       </c>
       <c r="M3">
-        <v>0.4155283</v>
+        <v>0.8310566</v>
       </c>
       <c r="N3">
-        <v>43.0844717</v>
+        <v>42.6689434</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>43.0844717</v>
+        <v>42.6689434</v>
       </c>
       <c r="Q3">
-        <v>61.0844717</v>
+        <v>60.6689434</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09100617020441992</v>
+        <v>0.09146745765548545</v>
       </c>
       <c r="T3">
-        <v>0.881152399484498</v>
+        <v>0.8901437504996458</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>104.6860105557191</v>
+        <v>52.34300527785954</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09064410850237573</v>
+        <v>0.09068910850237571</v>
       </c>
       <c r="C4">
-        <v>836.0192555842357</v>
+        <v>827.1176356775213</v>
       </c>
       <c r="D4">
-        <v>639.0412555842357</v>
+        <v>638.4006356775213</v>
       </c>
       <c r="E4">
-        <v>-91.878</v>
+        <v>-83.617</v>
       </c>
       <c r="F4">
-        <v>16.522</v>
+        <v>24.783</v>
       </c>
       <c r="G4">
         <v>213.5</v>
@@ -1603,28 +1603,28 @@
         <v>43.5</v>
       </c>
       <c r="M4">
-        <v>0.8310566</v>
+        <v>1.2465849</v>
       </c>
       <c r="N4">
-        <v>42.6689434</v>
+        <v>42.2534151</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>42.6689434</v>
+        <v>42.2534151</v>
       </c>
       <c r="Q4">
-        <v>60.6689434</v>
+        <v>60.2534151</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09146745765548545</v>
+        <v>0.09193825618801621</v>
       </c>
       <c r="T4">
-        <v>0.8901437504996458</v>
+        <v>0.8993204901955183</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>52.34300527785954</v>
+        <v>34.89533685190636</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09068910850237571</v>
+        <v>0.09073410850237573</v>
       </c>
       <c r="C5">
-        <v>827.1176356775213</v>
+        <v>818.2172988894334</v>
       </c>
       <c r="D5">
-        <v>638.4006356775213</v>
+        <v>637.7612988894334</v>
       </c>
       <c r="E5">
-        <v>-83.617</v>
+        <v>-75.35599999999999</v>
       </c>
       <c r="F5">
-        <v>24.783</v>
+        <v>33.044</v>
       </c>
       <c r="G5">
         <v>213.5</v>
@@ -1685,28 +1685,28 @@
         <v>43.5</v>
       </c>
       <c r="M5">
-        <v>1.2465849</v>
+        <v>1.6621132</v>
       </c>
       <c r="N5">
-        <v>42.2534151</v>
+        <v>41.8378868</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>42.2534151</v>
+        <v>41.8378868</v>
       </c>
       <c r="Q5">
-        <v>60.2534151</v>
+        <v>59.8378868</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09193825618801621</v>
+        <v>0.09241886302330805</v>
       </c>
       <c r="T5">
-        <v>0.8993204901955183</v>
+        <v>0.9086884119683885</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>34.89533685190636</v>
+        <v>26.17150263892977</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09073410850237573</v>
+        <v>0.09077910850237572</v>
       </c>
       <c r="C6">
-        <v>818.2172988894334</v>
+        <v>809.3182413688291</v>
       </c>
       <c r="D6">
-        <v>637.7612988894334</v>
+        <v>637.1232413688291</v>
       </c>
       <c r="E6">
-        <v>-75.35599999999999</v>
+        <v>-67.095</v>
       </c>
       <c r="F6">
-        <v>33.044</v>
+        <v>41.30500000000001</v>
       </c>
       <c r="G6">
         <v>213.5</v>
@@ -1767,28 +1767,28 @@
         <v>43.5</v>
       </c>
       <c r="M6">
-        <v>1.6621132</v>
+        <v>2.0776415</v>
       </c>
       <c r="N6">
-        <v>41.8378868</v>
+        <v>41.4223585</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>41.8378868</v>
+        <v>41.4223585</v>
       </c>
       <c r="Q6">
-        <v>59.8378868</v>
+        <v>59.4223585</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09241886302330805</v>
+        <v>0.09290958789723761</v>
       </c>
       <c r="T6">
-        <v>0.9086884119683885</v>
+        <v>0.918253553147003</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>26.17150263892977</v>
+        <v>20.93720211114381</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09077910850237572</v>
+        <v>0.09082410850237574</v>
       </c>
       <c r="C7">
-        <v>809.3182413688291</v>
+        <v>800.42045927996</v>
       </c>
       <c r="D7">
-        <v>637.1232413688291</v>
+        <v>636.4864592799601</v>
       </c>
       <c r="E7">
-        <v>-67.095</v>
+        <v>-58.834</v>
       </c>
       <c r="F7">
-        <v>41.30500000000001</v>
+        <v>49.566</v>
       </c>
       <c r="G7">
         <v>213.5</v>
@@ -1849,28 +1849,28 @@
         <v>43.5</v>
       </c>
       <c r="M7">
-        <v>2.0776415</v>
+        <v>2.4931698</v>
       </c>
       <c r="N7">
-        <v>41.4223585</v>
+        <v>41.0068302</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>41.4223585</v>
+        <v>41.0068302</v>
       </c>
       <c r="Q7">
-        <v>59.4223585</v>
+        <v>59.0068302</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09290958789723761</v>
+        <v>0.09341075372593163</v>
       </c>
       <c r="T7">
-        <v>0.918253553147003</v>
+        <v>0.9280222079677158</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.93720211114381</v>
+        <v>17.44766842595318</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09082410850237574</v>
+        <v>0.09086910850237573</v>
       </c>
       <c r="C8">
-        <v>800.42045927996</v>
+        <v>791.5239488023992</v>
       </c>
       <c r="D8">
-        <v>636.4864592799601</v>
+        <v>635.8509488023992</v>
       </c>
       <c r="E8">
-        <v>-58.834</v>
+        <v>-50.57300000000001</v>
       </c>
       <c r="F8">
-        <v>49.566</v>
+        <v>57.827</v>
       </c>
       <c r="G8">
         <v>213.5</v>
@@ -1931,28 +1931,28 @@
         <v>43.5</v>
       </c>
       <c r="M8">
-        <v>2.4931698</v>
+        <v>2.9086981</v>
       </c>
       <c r="N8">
-        <v>41.0068302</v>
+        <v>40.5913019</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>41.0068302</v>
+        <v>40.5913019</v>
       </c>
       <c r="Q8">
-        <v>59.0068302</v>
+        <v>58.5913019</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09341075372593163</v>
+        <v>0.09392269731438251</v>
       </c>
       <c r="T8">
-        <v>0.9280222079677158</v>
+        <v>0.9380009413867235</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.44766842595318</v>
+        <v>14.95514436510273</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09086910850237571</v>
+        <v>0.09091410850237573</v>
       </c>
       <c r="C9">
-        <v>791.5239488023993</v>
+        <v>782.6287061309608</v>
       </c>
       <c r="D9">
-        <v>635.8509488023993</v>
+        <v>635.2167061309608</v>
       </c>
       <c r="E9">
-        <v>-50.573</v>
+        <v>-42.312</v>
       </c>
       <c r="F9">
-        <v>57.82700000000001</v>
+        <v>66.08800000000001</v>
       </c>
       <c r="G9">
         <v>213.5</v>
@@ -2013,28 +2013,28 @@
         <v>43.5</v>
       </c>
       <c r="M9">
-        <v>2.9086981</v>
+        <v>3.3242264</v>
       </c>
       <c r="N9">
-        <v>40.5913019</v>
+        <v>40.1757736</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>40.5913019</v>
+        <v>40.1757736</v>
       </c>
       <c r="Q9">
-        <v>58.5913019</v>
+        <v>58.1757736</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09392269731438251</v>
+        <v>0.09444577011127797</v>
       </c>
       <c r="T9">
-        <v>0.9380009413867235</v>
+        <v>0.9481966037931009</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.95514436510272</v>
+        <v>13.08575131946488</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09091410850237573</v>
+        <v>0.09109410850237573</v>
       </c>
       <c r="C10">
-        <v>782.6287061309608</v>
+        <v>771.8433379320022</v>
       </c>
       <c r="D10">
-        <v>635.2167061309608</v>
+        <v>632.6923379320023</v>
       </c>
       <c r="E10">
-        <v>-42.312</v>
+        <v>-34.051</v>
       </c>
       <c r="F10">
-        <v>66.08800000000001</v>
+        <v>74.349</v>
       </c>
       <c r="G10">
         <v>213.5</v>
@@ -2095,45 +2095,45 @@
         <v>43.5</v>
       </c>
       <c r="M10">
-        <v>3.3242264</v>
+        <v>3.8512782</v>
       </c>
       <c r="N10">
-        <v>40.1757736</v>
+        <v>39.6487218</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>40.1757736</v>
+        <v>39.6487218</v>
       </c>
       <c r="Q10">
-        <v>58.1757736</v>
+        <v>57.6487218</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09444577011127797</v>
+        <v>0.0949803390135997</v>
       </c>
       <c r="T10">
-        <v>0.9481966037931009</v>
+        <v>0.9586163466919263</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.08575131946488</v>
+        <v>11.29495137484485</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09109410850237573</v>
+        <v>0.09115410850237574</v>
       </c>
       <c r="C11">
-        <v>771.8433379320022</v>
+        <v>762.7453345925159</v>
       </c>
       <c r="D11">
-        <v>632.6923379320023</v>
+        <v>631.8553345925159</v>
       </c>
       <c r="E11">
-        <v>-34.051</v>
+        <v>-25.79000000000001</v>
       </c>
       <c r="F11">
-        <v>74.349</v>
+        <v>82.61</v>
       </c>
       <c r="G11">
         <v>213.5</v>
@@ -2177,28 +2177,28 @@
         <v>43.5</v>
       </c>
       <c r="M11">
-        <v>3.8512782</v>
+        <v>4.279198</v>
       </c>
       <c r="N11">
-        <v>39.6487218</v>
+        <v>39.220802</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>39.6487218</v>
+        <v>39.220802</v>
       </c>
       <c r="Q11">
-        <v>57.6487218</v>
+        <v>57.220802</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0949803390135997</v>
+        <v>0.09552678722486192</v>
       </c>
       <c r="T11">
-        <v>0.9586163466919263</v>
+        <v>0.9692676394329477</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.29495137484485</v>
+        <v>10.16545623736036</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09115410850237574</v>
+        <v>0.09140110850237575</v>
       </c>
       <c r="C12">
-        <v>762.7453345925159</v>
+        <v>751.0618680611105</v>
       </c>
       <c r="D12">
-        <v>631.8553345925159</v>
+        <v>628.4328680611105</v>
       </c>
       <c r="E12">
-        <v>-25.78999999999999</v>
+        <v>-17.529</v>
       </c>
       <c r="F12">
-        <v>82.61000000000001</v>
+        <v>90.87100000000001</v>
       </c>
       <c r="G12">
         <v>213.5</v>
@@ -2259,45 +2259,45 @@
         <v>43.5</v>
       </c>
       <c r="M12">
-        <v>4.279198000000001</v>
+        <v>4.8615985</v>
       </c>
       <c r="N12">
-        <v>39.220802</v>
+        <v>38.6384015</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>39.220802</v>
+        <v>38.6384015</v>
       </c>
       <c r="Q12">
-        <v>57.220802</v>
+        <v>56.6384015</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09552678722486192</v>
+        <v>0.0960855151712087</v>
       </c>
       <c r="T12">
-        <v>0.9692676394329477</v>
+        <v>0.9801582870670258</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.16545623736036</v>
+        <v>8.947674309180407</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09140110850237575</v>
+        <v>0.09147810850237573</v>
       </c>
       <c r="C13">
-        <v>751.0618680611105</v>
+        <v>741.7415131003381</v>
       </c>
       <c r="D13">
-        <v>628.4328680611105</v>
+        <v>627.3735131003381</v>
       </c>
       <c r="E13">
-        <v>-17.529</v>
+        <v>-9.268000000000001</v>
       </c>
       <c r="F13">
-        <v>90.87100000000001</v>
+        <v>99.13200000000001</v>
       </c>
       <c r="G13">
         <v>213.5</v>
@@ -2341,28 +2341,28 @@
         <v>43.5</v>
       </c>
       <c r="M13">
-        <v>4.8615985</v>
+        <v>5.303562</v>
       </c>
       <c r="N13">
-        <v>38.6384015</v>
+        <v>38.196438</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>38.6384015</v>
+        <v>38.196438</v>
       </c>
       <c r="Q13">
-        <v>56.6384015</v>
+        <v>56.196438</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0960855151712087</v>
+        <v>0.09665694147997242</v>
       </c>
       <c r="T13">
-        <v>0.9801582870670258</v>
+        <v>0.99129644942006</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.947674309180407</v>
+        <v>8.202034783415371</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09147810850237573</v>
+        <v>0.09165910850237573</v>
       </c>
       <c r="C14">
-        <v>741.7415131003381</v>
+        <v>731.0043505760432</v>
       </c>
       <c r="D14">
-        <v>627.3735131003381</v>
+        <v>624.8973505760432</v>
       </c>
       <c r="E14">
-        <v>-9.268000000000001</v>
+        <v>-1.007000000000005</v>
       </c>
       <c r="F14">
-        <v>99.13200000000001</v>
+        <v>107.393</v>
       </c>
       <c r="G14">
         <v>213.5</v>
@@ -2423,45 +2423,45 @@
         <v>43.5</v>
       </c>
       <c r="M14">
-        <v>5.303562</v>
+        <v>5.8314399</v>
       </c>
       <c r="N14">
-        <v>38.196438</v>
+        <v>37.6685601</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>38.196438</v>
+        <v>37.6685601</v>
       </c>
       <c r="Q14">
-        <v>56.196438</v>
+        <v>55.6685601</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09665694147997242</v>
+        <v>0.09724150402571922</v>
       </c>
       <c r="T14">
-        <v>0.99129644942006</v>
+        <v>1.00269066148236</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>8.202034783415371</v>
+        <v>7.459564146412621</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09165910850237573</v>
+        <v>0.09174410850237573</v>
       </c>
       <c r="C15">
-        <v>731.0043505760432</v>
+        <v>721.5872442431448</v>
       </c>
       <c r="D15">
-        <v>624.8973505760432</v>
+        <v>623.7412442431448</v>
       </c>
       <c r="E15">
-        <v>-1.007000000000005</v>
+        <v>7.254000000000005</v>
       </c>
       <c r="F15">
-        <v>107.393</v>
+        <v>115.654</v>
       </c>
       <c r="G15">
         <v>213.5</v>
@@ -2505,28 +2505,28 @@
         <v>43.5</v>
       </c>
       <c r="M15">
-        <v>5.8314399</v>
+        <v>6.280012200000001</v>
       </c>
       <c r="N15">
-        <v>37.6685601</v>
+        <v>37.2199878</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>37.6685601</v>
+        <v>37.2199878</v>
       </c>
       <c r="Q15">
-        <v>55.6685601</v>
+        <v>55.2199878</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09724150402571922</v>
+        <v>0.09783966104927411</v>
       </c>
       <c r="T15">
-        <v>1.00269066148236</v>
+        <v>1.014349855220527</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.459564146412621</v>
+        <v>6.926738135954576</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09174410850237573</v>
+        <v>0.09182910850237572</v>
       </c>
       <c r="C16">
-        <v>721.5872442431448</v>
+        <v>712.1744077751862</v>
       </c>
       <c r="D16">
-        <v>623.7412442431448</v>
+        <v>622.5894077751861</v>
       </c>
       <c r="E16">
-        <v>7.254000000000005</v>
+        <v>15.51500000000001</v>
       </c>
       <c r="F16">
-        <v>115.654</v>
+        <v>123.915</v>
       </c>
       <c r="G16">
         <v>213.5</v>
@@ -2587,28 +2587,28 @@
         <v>43.5</v>
       </c>
       <c r="M16">
-        <v>6.280012200000001</v>
+        <v>6.728584500000001</v>
       </c>
       <c r="N16">
-        <v>37.2199878</v>
+        <v>36.7714155</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>37.2199878</v>
+        <v>36.7714155</v>
       </c>
       <c r="Q16">
-        <v>55.2199878</v>
+        <v>54.7714155</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09783966104927411</v>
+        <v>0.09845189235573615</v>
       </c>
       <c r="T16">
-        <v>1.014349855220527</v>
+        <v>1.026283382929003</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.926738135954576</v>
+        <v>6.464955593557604</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09182910850237572</v>
+        <v>0.09207410850237571</v>
       </c>
       <c r="C17">
-        <v>712.1744077751862</v>
+        <v>700.6170848455486</v>
       </c>
       <c r="D17">
-        <v>622.5894077751861</v>
+        <v>619.2930848455486</v>
       </c>
       <c r="E17">
-        <v>15.51499999999999</v>
+        <v>23.77600000000001</v>
       </c>
       <c r="F17">
-        <v>123.915</v>
+        <v>132.176</v>
       </c>
       <c r="G17">
         <v>213.5</v>
@@ -2669,45 +2669,45 @@
         <v>43.5</v>
       </c>
       <c r="M17">
-        <v>6.728584499999999</v>
+        <v>7.309332800000001</v>
       </c>
       <c r="N17">
-        <v>36.7714155</v>
+        <v>36.1906672</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>36.7714155</v>
+        <v>36.1906672</v>
       </c>
       <c r="Q17">
-        <v>54.7714155</v>
+        <v>54.1906672</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09845189235573615</v>
+        <v>0.09907870059806634</v>
       </c>
       <c r="T17">
-        <v>1.026283382929003</v>
+        <v>1.038501042249587</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.464955593557606</v>
+        <v>5.951295581998948</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09207410850237571</v>
+        <v>0.09216910850237574</v>
       </c>
       <c r="C18">
-        <v>700.6170848455486</v>
+        <v>691.0872909230317</v>
       </c>
       <c r="D18">
-        <v>619.2930848455486</v>
+        <v>618.0242909230317</v>
       </c>
       <c r="E18">
-        <v>23.77600000000001</v>
+        <v>32.03700000000001</v>
       </c>
       <c r="F18">
-        <v>132.176</v>
+        <v>140.437</v>
       </c>
       <c r="G18">
         <v>213.5</v>
@@ -2751,28 +2751,28 @@
         <v>43.5</v>
       </c>
       <c r="M18">
-        <v>7.309332800000001</v>
+        <v>7.766166100000001</v>
       </c>
       <c r="N18">
-        <v>36.1906672</v>
+        <v>35.7338339</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>36.1906672</v>
+        <v>35.7338339</v>
       </c>
       <c r="Q18">
-        <v>54.1906672</v>
+        <v>53.7338339</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09907870059806634</v>
+        <v>0.09972061265346474</v>
       </c>
       <c r="T18">
-        <v>1.038501042249587</v>
+        <v>1.051013102999582</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.951295581998948</v>
+        <v>5.601219371293126</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09216910850237574</v>
+        <v>0.09226410850237574</v>
       </c>
       <c r="C19">
-        <v>691.0872909230317</v>
+        <v>681.5626853244289</v>
       </c>
       <c r="D19">
-        <v>618.0242909230317</v>
+        <v>616.7606853244289</v>
       </c>
       <c r="E19">
-        <v>32.03700000000001</v>
+        <v>40.298</v>
       </c>
       <c r="F19">
-        <v>140.437</v>
+        <v>148.698</v>
       </c>
       <c r="G19">
         <v>213.5</v>
@@ -2833,28 +2833,28 @@
         <v>43.5</v>
       </c>
       <c r="M19">
-        <v>7.766166100000001</v>
+        <v>8.222999400000001</v>
       </c>
       <c r="N19">
-        <v>35.7338339</v>
+        <v>35.2770006</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>35.7338339</v>
+        <v>35.2770006</v>
       </c>
       <c r="Q19">
-        <v>53.7338339</v>
+        <v>53.2770006</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09972061265346474</v>
+        <v>0.1003781811004582</v>
       </c>
       <c r="T19">
-        <v>1.051013102999582</v>
+        <v>1.063830335962991</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.601219371293126</v>
+        <v>5.290040517332398</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09226410850237574</v>
+        <v>0.09235910850237572</v>
       </c>
       <c r="C20">
-        <v>681.5626853244289</v>
+        <v>672.0432362907061</v>
       </c>
       <c r="D20">
-        <v>616.7606853244289</v>
+        <v>615.502236290706</v>
       </c>
       <c r="E20">
-        <v>40.298</v>
+        <v>48.559</v>
       </c>
       <c r="F20">
-        <v>148.698</v>
+        <v>156.959</v>
       </c>
       <c r="G20">
         <v>213.5</v>
@@ -2915,28 +2915,28 @@
         <v>43.5</v>
       </c>
       <c r="M20">
-        <v>8.222999400000001</v>
+        <v>8.6798327</v>
       </c>
       <c r="N20">
-        <v>35.2770006</v>
+        <v>34.8201673</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>35.2770006</v>
+        <v>34.8201673</v>
       </c>
       <c r="Q20">
-        <v>53.2770006</v>
+        <v>52.8201673</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1003781811004582</v>
+        <v>0.1010519858054021</v>
       </c>
       <c r="T20">
-        <v>1.063830335962991</v>
+        <v>1.076964043814386</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.290040517332398</v>
+        <v>5.01161733220964</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09235910850237572</v>
+        <v>0.09245410850237573</v>
       </c>
       <c r="C21">
-        <v>672.0432362907061</v>
+        <v>662.5289123215074</v>
       </c>
       <c r="D21">
-        <v>615.502236290706</v>
+        <v>614.2489123215074</v>
       </c>
       <c r="E21">
-        <v>48.559</v>
+        <v>56.82000000000002</v>
       </c>
       <c r="F21">
-        <v>156.959</v>
+        <v>165.22</v>
       </c>
       <c r="G21">
         <v>213.5</v>
@@ -2997,28 +2997,28 @@
         <v>43.5</v>
       </c>
       <c r="M21">
-        <v>8.6798327</v>
+        <v>9.136666000000002</v>
       </c>
       <c r="N21">
-        <v>34.8201673</v>
+        <v>34.36333399999999</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>34.8201673</v>
+        <v>34.36333399999999</v>
       </c>
       <c r="Q21">
-        <v>52.8201673</v>
+        <v>52.36333399999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1010519858054021</v>
+        <v>0.1017426356279697</v>
       </c>
       <c r="T21">
-        <v>1.076964043814386</v>
+        <v>1.090426094362066</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.01161733220964</v>
+        <v>4.761036465599157</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09245410850237573</v>
+        <v>0.09254910850237573</v>
       </c>
       <c r="C22">
-        <v>662.5289123215074</v>
+        <v>653.0196821725287</v>
       </c>
       <c r="D22">
-        <v>614.2489123215074</v>
+        <v>613.0006821725287</v>
       </c>
       <c r="E22">
-        <v>56.82000000000002</v>
+        <v>65.08100000000002</v>
       </c>
       <c r="F22">
-        <v>165.22</v>
+        <v>173.481</v>
       </c>
       <c r="G22">
         <v>213.5</v>
@@ -3079,28 +3079,28 @@
         <v>43.5</v>
       </c>
       <c r="M22">
-        <v>9.136666000000002</v>
+        <v>9.593499300000001</v>
       </c>
       <c r="N22">
-        <v>34.36333399999999</v>
+        <v>33.9065007</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>34.36333399999999</v>
+        <v>33.9065007</v>
       </c>
       <c r="Q22">
-        <v>52.36333399999999</v>
+        <v>51.9065007</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1017426356279697</v>
+        <v>0.1024507702561718</v>
       </c>
       <c r="T22">
-        <v>1.090426094362066</v>
+        <v>1.104228956316016</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.761036465599157</v>
+        <v>4.534320443427768</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09254910850237573</v>
+        <v>0.09319410850237572</v>
       </c>
       <c r="C23">
-        <v>653.0196821725287</v>
+        <v>636.4161802773519</v>
       </c>
       <c r="D23">
-        <v>613.0006821725287</v>
+        <v>604.658180277352</v>
       </c>
       <c r="E23">
-        <v>65.08099999999999</v>
+        <v>73.34200000000001</v>
       </c>
       <c r="F23">
-        <v>173.481</v>
+        <v>181.742</v>
       </c>
       <c r="G23">
         <v>213.5</v>
@@ -3161,45 +3161,45 @@
         <v>43.5</v>
       </c>
       <c r="M23">
-        <v>9.5934993</v>
+        <v>10.5046876</v>
       </c>
       <c r="N23">
-        <v>33.9065007</v>
+        <v>32.9953124</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>33.9065007</v>
+        <v>32.9953124</v>
       </c>
       <c r="Q23">
-        <v>51.9065007</v>
+        <v>50.9953124</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1024507702561718</v>
+        <v>0.103177062182533</v>
       </c>
       <c r="T23">
-        <v>1.104228956316016</v>
+        <v>1.118385737807247</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.53432044342777</v>
+        <v>4.141008438937298</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09319410850237572</v>
+        <v>0.09411910850237573</v>
       </c>
       <c r="C24">
-        <v>636.4161802773519</v>
+        <v>616.5798670298186</v>
       </c>
       <c r="D24">
-        <v>604.658180277352</v>
+        <v>593.0828670298187</v>
       </c>
       <c r="E24">
-        <v>73.34200000000001</v>
+        <v>81.60300000000001</v>
       </c>
       <c r="F24">
-        <v>181.742</v>
+        <v>190.003</v>
       </c>
       <c r="G24">
         <v>213.5</v>
@@ -3243,45 +3243,45 @@
         <v>43.5</v>
       </c>
       <c r="M24">
-        <v>10.5046876</v>
+        <v>11.6471839</v>
       </c>
       <c r="N24">
-        <v>32.9953124</v>
+        <v>31.8528161</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>32.9953124</v>
+        <v>31.8528161</v>
       </c>
       <c r="Q24">
-        <v>50.9953124</v>
+        <v>49.8528161</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.103177062182533</v>
+        <v>0.1039222188342542</v>
       </c>
       <c r="T24">
-        <v>1.118385737807247</v>
+        <v>1.13291022790864</v>
       </c>
       <c r="U24">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.141008438937298</v>
+        <v>3.734808377156301</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09411910850237573</v>
+        <v>0.09427410850237573</v>
       </c>
       <c r="C25">
-        <v>616.5798670298186</v>
+        <v>606.4224351566029</v>
       </c>
       <c r="D25">
-        <v>593.0828670298187</v>
+        <v>591.1864351566029</v>
       </c>
       <c r="E25">
-        <v>81.60300000000001</v>
+        <v>89.864</v>
       </c>
       <c r="F25">
-        <v>190.003</v>
+        <v>198.264</v>
       </c>
       <c r="G25">
         <v>213.5</v>
@@ -3325,28 +3325,28 @@
         <v>43.5</v>
       </c>
       <c r="M25">
-        <v>11.6471839</v>
+        <v>12.1535832</v>
       </c>
       <c r="N25">
-        <v>31.8528161</v>
+        <v>31.3464168</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>31.8528161</v>
+        <v>31.3464168</v>
       </c>
       <c r="Q25">
-        <v>49.8528161</v>
+        <v>49.3464168</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1039222188342542</v>
+        <v>0.104686984871547</v>
       </c>
       <c r="T25">
-        <v>1.13291022790864</v>
+        <v>1.147816941433754</v>
       </c>
       <c r="U25">
         <v>0.0613</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.734808377156301</v>
+        <v>3.579191361441455</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09427410850237573</v>
+        <v>0.09512910850237573</v>
       </c>
       <c r="C26">
-        <v>606.4224351566029</v>
+        <v>587.9146575965635</v>
       </c>
       <c r="D26">
-        <v>591.1864351566029</v>
+        <v>580.9396575965635</v>
       </c>
       <c r="E26">
-        <v>89.864</v>
+        <v>98.125</v>
       </c>
       <c r="F26">
-        <v>198.264</v>
+        <v>206.525</v>
       </c>
       <c r="G26">
         <v>213.5</v>
@@ -3407,45 +3407,45 @@
         <v>43.5</v>
       </c>
       <c r="M26">
-        <v>12.1535832</v>
+        <v>13.2382525</v>
       </c>
       <c r="N26">
-        <v>31.3464168</v>
+        <v>30.2617475</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>31.3464168</v>
+        <v>30.2617475</v>
       </c>
       <c r="Q26">
-        <v>49.3464168</v>
+        <v>48.2617475</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.104686984871547</v>
+        <v>0.1054721446698343</v>
       </c>
       <c r="T26">
-        <v>1.147816941433754</v>
+        <v>1.163121167319537</v>
       </c>
       <c r="U26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.579191361441455</v>
+        <v>3.285932187801977</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09512910850237573</v>
+        <v>0.09531210850237573</v>
       </c>
       <c r="C27">
-        <v>587.9146575965635</v>
+        <v>577.5064665244024</v>
       </c>
       <c r="D27">
-        <v>580.9396575965635</v>
+        <v>578.7924665244024</v>
       </c>
       <c r="E27">
-        <v>98.125</v>
+        <v>106.386</v>
       </c>
       <c r="F27">
-        <v>206.525</v>
+        <v>214.786</v>
       </c>
       <c r="G27">
         <v>213.5</v>
@@ -3489,28 +3489,28 @@
         <v>43.5</v>
       </c>
       <c r="M27">
-        <v>13.2382525</v>
+        <v>13.7677826</v>
       </c>
       <c r="N27">
-        <v>30.2617475</v>
+        <v>29.7322174</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>30.2617475</v>
+        <v>29.7322174</v>
       </c>
       <c r="Q27">
-        <v>48.2617475</v>
+        <v>47.7322174</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1054721446698343</v>
+        <v>0.1062785250032104</v>
       </c>
       <c r="T27">
-        <v>1.163121167319537</v>
+        <v>1.178839020931963</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.285932187801977</v>
+        <v>3.159550180578825</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09531210850237573</v>
+        <v>0.09549510850237573</v>
       </c>
       <c r="C28">
-        <v>577.5064665244024</v>
+        <v>567.1140893211731</v>
       </c>
       <c r="D28">
-        <v>578.7924665244024</v>
+        <v>576.6610893211731</v>
       </c>
       <c r="E28">
-        <v>106.386</v>
+        <v>114.647</v>
       </c>
       <c r="F28">
-        <v>214.786</v>
+        <v>223.047</v>
       </c>
       <c r="G28">
         <v>213.5</v>
@@ -3571,28 +3571,28 @@
         <v>43.5</v>
       </c>
       <c r="M28">
-        <v>13.7677826</v>
+        <v>14.2973127</v>
       </c>
       <c r="N28">
-        <v>29.7322174</v>
+        <v>29.2026873</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>29.7322174</v>
+        <v>29.2026873</v>
       </c>
       <c r="Q28">
-        <v>47.7322174</v>
+        <v>47.20268729999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1062785250032104</v>
+        <v>0.1071069979484599</v>
       </c>
       <c r="T28">
-        <v>1.178839020931963</v>
+        <v>1.194987500670758</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.159550180578825</v>
+        <v>3.042529803520349</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09549510850237573</v>
+        <v>0.09786210850237573</v>
       </c>
       <c r="C29">
-        <v>567.1140893211731</v>
+        <v>532.635234576375</v>
       </c>
       <c r="D29">
-        <v>576.6610893211731</v>
+        <v>550.4432345763749</v>
       </c>
       <c r="E29">
-        <v>114.647</v>
+        <v>122.908</v>
       </c>
       <c r="F29">
-        <v>223.047</v>
+        <v>231.308</v>
       </c>
       <c r="G29">
         <v>213.5</v>
@@ -3653,45 +3653,45 @@
         <v>43.5</v>
       </c>
       <c r="M29">
-        <v>14.2973127</v>
+        <v>16.6310452</v>
       </c>
       <c r="N29">
-        <v>29.2026873</v>
+        <v>26.8689548</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>29.2026873</v>
+        <v>26.8689548</v>
       </c>
       <c r="Q29">
-        <v>47.20268729999999</v>
+        <v>44.8689548</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1071069979484599</v>
+        <v>0.1079584840310774</v>
       </c>
       <c r="T29">
-        <v>1.194987500670758</v>
+        <v>1.211584549291185</v>
       </c>
       <c r="U29">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V29">
         <v>0</v>
       </c>
       <c r="W29">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.042529803520349</v>
+        <v>2.615590269696338</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09786210850237573</v>
+        <v>0.09812310850237574</v>
       </c>
       <c r="C30">
-        <v>532.635234576375</v>
+        <v>521.6284939593411</v>
       </c>
       <c r="D30">
-        <v>550.4432345763749</v>
+        <v>547.6974939593412</v>
       </c>
       <c r="E30">
-        <v>122.908</v>
+        <v>131.169</v>
       </c>
       <c r="F30">
-        <v>231.308</v>
+        <v>239.569</v>
       </c>
       <c r="G30">
         <v>213.5</v>
@@ -3735,28 +3735,28 @@
         <v>43.5</v>
       </c>
       <c r="M30">
-        <v>16.6310452</v>
+        <v>17.2250111</v>
       </c>
       <c r="N30">
-        <v>26.8689548</v>
+        <v>26.2749889</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>26.8689548</v>
+        <v>26.2749889</v>
       </c>
       <c r="Q30">
-        <v>44.8689548</v>
+        <v>44.2749889</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1079584840310774</v>
+        <v>0.1088339556371489</v>
       </c>
       <c r="T30">
-        <v>1.211584549291185</v>
+        <v>1.228649120407962</v>
       </c>
       <c r="U30">
         <v>0.07190000000000001</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.615590269696338</v>
+        <v>2.525397501775775</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09812310850237571</v>
+        <v>0.09955410850237573</v>
       </c>
       <c r="C31">
-        <v>521.6284939593414</v>
+        <v>498.7871179528974</v>
       </c>
       <c r="D31">
-        <v>547.6974939593414</v>
+        <v>533.1171179528974</v>
       </c>
       <c r="E31">
-        <v>131.169</v>
+        <v>139.43</v>
       </c>
       <c r="F31">
-        <v>239.569</v>
+        <v>247.83</v>
       </c>
       <c r="G31">
         <v>213.5</v>
@@ -3817,45 +3817,45 @@
         <v>43.5</v>
       </c>
       <c r="M31">
-        <v>17.2250111</v>
+        <v>18.785514</v>
       </c>
       <c r="N31">
-        <v>26.2749889</v>
+        <v>24.714486</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>26.2749889</v>
+        <v>24.714486</v>
       </c>
       <c r="Q31">
-        <v>44.2749889</v>
+        <v>42.714486</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1088339556371489</v>
+        <v>0.1097344407176796</v>
       </c>
       <c r="T31">
-        <v>1.228649120407962</v>
+        <v>1.246201250699504</v>
       </c>
       <c r="U31">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V31">
         <v>0</v>
       </c>
       <c r="W31">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.525397501775775</v>
+        <v>2.315614041755791</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09955410850237573</v>
+        <v>0.09985410850237572</v>
       </c>
       <c r="C32">
-        <v>498.7871179528974</v>
+        <v>487.5673209286372</v>
       </c>
       <c r="D32">
-        <v>533.1171179528974</v>
+        <v>530.1583209286372</v>
       </c>
       <c r="E32">
-        <v>139.43</v>
+        <v>147.691</v>
       </c>
       <c r="F32">
-        <v>247.83</v>
+        <v>256.091</v>
       </c>
       <c r="G32">
         <v>213.5</v>
@@ -3899,28 +3899,28 @@
         <v>43.5</v>
       </c>
       <c r="M32">
-        <v>18.785514</v>
+        <v>19.4116978</v>
       </c>
       <c r="N32">
-        <v>24.714486</v>
+        <v>24.0883022</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>24.714486</v>
+        <v>24.0883022</v>
       </c>
       <c r="Q32">
-        <v>42.714486</v>
+        <v>42.0883022</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1097344407176796</v>
+        <v>0.1106610268150373</v>
       </c>
       <c r="T32">
-        <v>1.246201250699504</v>
+        <v>1.264262138390801</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.315614041755791</v>
+        <v>2.240916814602378</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09985410850237572</v>
+        <v>0.1001541085023757</v>
       </c>
       <c r="C33">
-        <v>487.5673209286372</v>
+        <v>476.3801852479896</v>
       </c>
       <c r="D33">
-        <v>530.1583209286372</v>
+        <v>527.2321852479896</v>
       </c>
       <c r="E33">
-        <v>147.691</v>
+        <v>155.952</v>
       </c>
       <c r="F33">
-        <v>256.091</v>
+        <v>264.352</v>
       </c>
       <c r="G33">
         <v>213.5</v>
@@ -3981,28 +3981,28 @@
         <v>43.5</v>
       </c>
       <c r="M33">
-        <v>19.4116978</v>
+        <v>20.03788160000001</v>
       </c>
       <c r="N33">
-        <v>24.0883022</v>
+        <v>23.46211839999999</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>24.0883022</v>
+        <v>23.46211839999999</v>
       </c>
       <c r="Q33">
-        <v>42.0883022</v>
+        <v>41.46211839999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1106610268150373</v>
+        <v>0.1116148654446702</v>
       </c>
       <c r="T33">
-        <v>1.264262138390801</v>
+        <v>1.282854228661254</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.240916814602378</v>
+        <v>2.170888164146054</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1001541085023757</v>
+        <v>0.1004541085023757</v>
       </c>
       <c r="C34">
-        <v>476.3801852479896</v>
+        <v>465.2251730701581</v>
       </c>
       <c r="D34">
-        <v>527.2321852479896</v>
+        <v>524.3381730701581</v>
       </c>
       <c r="E34">
-        <v>155.952</v>
+        <v>164.213</v>
       </c>
       <c r="F34">
-        <v>264.352</v>
+        <v>272.613</v>
       </c>
       <c r="G34">
         <v>213.5</v>
@@ -4063,28 +4063,28 @@
         <v>43.5</v>
       </c>
       <c r="M34">
-        <v>20.03788160000001</v>
+        <v>20.6640654</v>
       </c>
       <c r="N34">
-        <v>23.46211839999999</v>
+        <v>22.8359346</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>23.46211839999999</v>
+        <v>22.8359346</v>
       </c>
       <c r="Q34">
-        <v>41.46211839999999</v>
+        <v>40.8359346</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1116148654446702</v>
+        <v>0.1125971768692175</v>
       </c>
       <c r="T34">
-        <v>1.282854228661254</v>
+        <v>1.302001306700975</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.170888164146054</v>
+        <v>2.105103674323447</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1004541085023757</v>
+        <v>0.1007541085023757</v>
       </c>
       <c r="C35">
-        <v>465.2251730701581</v>
+        <v>454.1017582988542</v>
       </c>
       <c r="D35">
-        <v>524.3381730701581</v>
+        <v>521.4757582988542</v>
       </c>
       <c r="E35">
-        <v>164.213</v>
+        <v>172.474</v>
       </c>
       <c r="F35">
-        <v>272.613</v>
+        <v>280.874</v>
       </c>
       <c r="G35">
         <v>213.5</v>
@@ -4145,28 +4145,28 @@
         <v>43.5</v>
       </c>
       <c r="M35">
-        <v>20.6640654</v>
+        <v>21.29024920000001</v>
       </c>
       <c r="N35">
-        <v>22.8359346</v>
+        <v>22.20975079999999</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>22.8359346</v>
+        <v>22.20975079999999</v>
       </c>
       <c r="Q35">
-        <v>40.8359346</v>
+        <v>40.20975079999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1125971768692175</v>
+        <v>0.1136092553066299</v>
       </c>
       <c r="T35">
-        <v>1.302001306700975</v>
+        <v>1.321728599226747</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.105103674323447</v>
+        <v>2.043188860372756</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1007541085023757</v>
+        <v>0.1060241085023757</v>
       </c>
       <c r="C36">
-        <v>454.1017582988542</v>
+        <v>400.2082480869917</v>
       </c>
       <c r="D36">
-        <v>521.4757582988542</v>
+        <v>475.8432480869918</v>
       </c>
       <c r="E36">
-        <v>172.474</v>
+        <v>180.735</v>
       </c>
       <c r="F36">
-        <v>280.874</v>
+        <v>289.135</v>
       </c>
       <c r="G36">
         <v>213.5</v>
@@ -4227,45 +4227,45 @@
         <v>43.5</v>
       </c>
       <c r="M36">
-        <v>21.29024920000001</v>
+        <v>26.02215</v>
       </c>
       <c r="N36">
-        <v>22.20975079999999</v>
+        <v>17.47785</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>22.20975079999999</v>
+        <v>17.47785</v>
       </c>
       <c r="Q36">
-        <v>40.20975079999999</v>
+        <v>35.47785</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1136092553066299</v>
+        <v>0.1146524746190396</v>
       </c>
       <c r="T36">
-        <v>1.321728599226747</v>
+        <v>1.342062885368697</v>
       </c>
       <c r="U36">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V36">
         <v>0</v>
       </c>
       <c r="W36">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.043188860372756</v>
+        <v>1.671652803477038</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1060241085023757</v>
+        <v>0.1064661085023757</v>
       </c>
       <c r="C37">
-        <v>400.2082480869917</v>
+        <v>388.4803582394879</v>
       </c>
       <c r="D37">
-        <v>475.8432480869918</v>
+        <v>472.376358239488</v>
       </c>
       <c r="E37">
-        <v>180.735</v>
+        <v>188.996</v>
       </c>
       <c r="F37">
-        <v>289.135</v>
+        <v>297.396</v>
       </c>
       <c r="G37">
         <v>213.5</v>
@@ -4309,28 +4309,28 @@
         <v>43.5</v>
       </c>
       <c r="M37">
-        <v>26.02215</v>
+        <v>26.76564</v>
       </c>
       <c r="N37">
-        <v>17.47785</v>
+        <v>16.73436</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>17.47785</v>
+        <v>16.73436</v>
       </c>
       <c r="Q37">
-        <v>35.47785</v>
+        <v>34.73436</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1146524746190396</v>
+        <v>0.1157282945349621</v>
       </c>
       <c r="T37">
-        <v>1.342062885368697</v>
+        <v>1.363032617952583</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.671652803477038</v>
+        <v>1.625218003380454</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1064661085023757</v>
+        <v>0.1069081085023757</v>
       </c>
       <c r="C38">
-        <v>388.4803582394879</v>
+        <v>376.8026209936651</v>
       </c>
       <c r="D38">
-        <v>472.376358239488</v>
+        <v>468.9596209936651</v>
       </c>
       <c r="E38">
-        <v>188.996</v>
+        <v>197.257</v>
       </c>
       <c r="F38">
-        <v>297.396</v>
+        <v>305.657</v>
       </c>
       <c r="G38">
         <v>213.5</v>
@@ -4391,28 +4391,28 @@
         <v>43.5</v>
       </c>
       <c r="M38">
-        <v>26.76564</v>
+        <v>27.50913</v>
       </c>
       <c r="N38">
-        <v>16.73436</v>
+        <v>15.99087</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>16.73436</v>
+        <v>15.99087</v>
       </c>
       <c r="Q38">
-        <v>34.73436</v>
+        <v>33.99087</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1157282945349621</v>
+        <v>0.1168382674640885</v>
       </c>
       <c r="T38">
-        <v>1.363032617952583</v>
+        <v>1.384668056332782</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.625218003380454</v>
+        <v>1.581293192478279</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1069081085023757</v>
+        <v>0.1073501085023757</v>
       </c>
       <c r="C39">
-        <v>376.8026209936651</v>
+        <v>365.1739558908295</v>
       </c>
       <c r="D39">
-        <v>468.9596209936651</v>
+        <v>465.5919558908295</v>
       </c>
       <c r="E39">
-        <v>197.257</v>
+        <v>205.518</v>
       </c>
       <c r="F39">
-        <v>305.657</v>
+        <v>313.918</v>
       </c>
       <c r="G39">
         <v>213.5</v>
@@ -4473,28 +4473,28 @@
         <v>43.5</v>
       </c>
       <c r="M39">
-        <v>27.50913</v>
+        <v>28.25262</v>
       </c>
       <c r="N39">
-        <v>15.99087</v>
+        <v>15.24738</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>15.99087</v>
+        <v>15.24738</v>
       </c>
       <c r="Q39">
-        <v>33.99087</v>
+        <v>33.24738</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1168382674640885</v>
+        <v>0.1179840459715737</v>
       </c>
       <c r="T39">
-        <v>1.384668056332782</v>
+        <v>1.407001412080085</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.581293192478279</v>
+        <v>1.539680213728851</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1073501085023757</v>
+        <v>0.1077921085023757</v>
       </c>
       <c r="C40">
-        <v>365.1739558908295</v>
+        <v>353.5933132867089</v>
       </c>
       <c r="D40">
-        <v>465.5919558908295</v>
+        <v>462.2723132867089</v>
       </c>
       <c r="E40">
-        <v>205.518</v>
+        <v>213.779</v>
       </c>
       <c r="F40">
-        <v>313.918</v>
+        <v>322.179</v>
       </c>
       <c r="G40">
         <v>213.5</v>
@@ -4555,28 +4555,28 @@
         <v>43.5</v>
       </c>
       <c r="M40">
-        <v>28.25262</v>
+        <v>28.99611</v>
       </c>
       <c r="N40">
-        <v>15.24738</v>
+        <v>14.50389</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>15.24738</v>
+        <v>14.50389</v>
       </c>
       <c r="Q40">
-        <v>33.24738</v>
+        <v>32.50389</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1179840459715737</v>
+        <v>0.1191673909875012</v>
       </c>
       <c r="T40">
-        <v>1.407001412080085</v>
+        <v>1.430067008999431</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.539680213728851</v>
+        <v>1.500201233889649</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1077921085023757</v>
+        <v>0.1309541085023757</v>
       </c>
       <c r="C41">
-        <v>353.5933132867089</v>
+        <v>219.593796277303</v>
       </c>
       <c r="D41">
-        <v>462.2723132867089</v>
+        <v>336.5337962773031</v>
       </c>
       <c r="E41">
-        <v>213.779</v>
+        <v>222.04</v>
       </c>
       <c r="F41">
-        <v>322.179</v>
+        <v>330.4400000000001</v>
       </c>
       <c r="G41">
         <v>213.5</v>
@@ -4637,45 +4637,45 @@
         <v>43.5</v>
       </c>
       <c r="M41">
-        <v>28.99611</v>
+        <v>48.50859200000001</v>
       </c>
       <c r="N41">
-        <v>14.50389</v>
+        <v>-5.008592000000014</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P41">
-        <v>14.50389</v>
+        <v>-5.008592000000014</v>
       </c>
       <c r="Q41">
-        <v>32.50389</v>
+        <v>12.99140799999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1191673909875012</v>
+        <v>0.1203901808372929</v>
       </c>
       <c r="T41">
-        <v>1.430067008999431</v>
+        <v>1.453901459149421</v>
       </c>
       <c r="U41">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V41">
         <v>0</v>
       </c>
       <c r="W41">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y41">
-        <v>1.500201233889649</v>
+        <v>0.8967483533638739</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1309541085023757</v>
+        <v>0.1319641085023757</v>
       </c>
       <c r="C42">
-        <v>219.593796277303</v>
+        <v>207.3880083586687</v>
       </c>
       <c r="D42">
-        <v>336.5337962773031</v>
+        <v>332.5890083586688</v>
       </c>
       <c r="E42">
-        <v>222.04</v>
+        <v>230.301</v>
       </c>
       <c r="F42">
-        <v>330.4400000000001</v>
+        <v>338.701</v>
       </c>
       <c r="G42">
         <v>213.5</v>
@@ -4719,28 +4719,28 @@
         <v>43.5</v>
       </c>
       <c r="M42">
-        <v>48.50859200000001</v>
+        <v>49.72130680000001</v>
       </c>
       <c r="N42">
-        <v>-5.008592000000014</v>
+        <v>-6.221306800000008</v>
       </c>
       <c r="O42">
         <v>-0</v>
       </c>
       <c r="P42">
-        <v>-5.008592000000014</v>
+        <v>-6.221306800000008</v>
       </c>
       <c r="Q42">
-        <v>12.99140799999999</v>
+        <v>11.77869319999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1203901808372929</v>
+        <v>0.1216544211904673</v>
       </c>
       <c r="T42">
-        <v>1.453901459149421</v>
+        <v>1.478543856762123</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8967483533638739</v>
+        <v>0.8748764423062185</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1319641085023757</v>
+        <v>0.1329741085023757</v>
       </c>
       <c r="C43">
-        <v>207.3880083586687</v>
+        <v>195.2736291361774</v>
       </c>
       <c r="D43">
-        <v>332.5890083586688</v>
+        <v>328.7356291361774</v>
       </c>
       <c r="E43">
-        <v>230.301</v>
+        <v>238.562</v>
       </c>
       <c r="F43">
-        <v>338.701</v>
+        <v>346.962</v>
       </c>
       <c r="G43">
         <v>213.5</v>
@@ -4801,28 +4801,28 @@
         <v>43.5</v>
       </c>
       <c r="M43">
-        <v>49.72130680000001</v>
+        <v>50.93402160000001</v>
       </c>
       <c r="N43">
-        <v>-6.221306800000008</v>
+        <v>-7.434021600000008</v>
       </c>
       <c r="O43">
         <v>-0</v>
       </c>
       <c r="P43">
-        <v>-6.221306800000008</v>
+        <v>-7.434021600000008</v>
       </c>
       <c r="Q43">
-        <v>11.77869319999999</v>
+        <v>10.56597839999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1216544211904673</v>
+        <v>0.1229622560385789</v>
       </c>
       <c r="T43">
-        <v>1.478543856762123</v>
+        <v>1.50403599222354</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8748764423062185</v>
+        <v>0.8540460508227372</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1329741085023757</v>
+        <v>0.1339841085023757</v>
       </c>
       <c r="C44">
-        <v>195.2736291361774</v>
+        <v>183.247517813216</v>
       </c>
       <c r="D44">
-        <v>328.7356291361774</v>
+        <v>324.9705178132161</v>
       </c>
       <c r="E44">
-        <v>238.562</v>
+        <v>246.823</v>
       </c>
       <c r="F44">
-        <v>346.962</v>
+        <v>355.223</v>
       </c>
       <c r="G44">
         <v>213.5</v>
@@ -4883,28 +4883,28 @@
         <v>43.5</v>
       </c>
       <c r="M44">
-        <v>50.9340216</v>
+        <v>52.14673640000001</v>
       </c>
       <c r="N44">
-        <v>-7.434021600000001</v>
+        <v>-8.646736400000009</v>
       </c>
       <c r="O44">
         <v>-0</v>
       </c>
       <c r="P44">
-        <v>-7.434021600000001</v>
+        <v>-8.646736400000009</v>
       </c>
       <c r="Q44">
-        <v>10.5659784</v>
+        <v>9.353263599999991</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1229622560385788</v>
+        <v>0.1243159798287293</v>
       </c>
       <c r="T44">
-        <v>1.504035992223539</v>
+        <v>1.530422588578338</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8540460508227373</v>
+        <v>0.8341845147570921</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1339841085023757</v>
+        <v>0.1349941085023758</v>
       </c>
       <c r="C45">
-        <v>183.247517813216</v>
+        <v>171.3066758538943</v>
       </c>
       <c r="D45">
-        <v>324.9705178132161</v>
+        <v>321.2906758538942</v>
       </c>
       <c r="E45">
-        <v>246.823</v>
+        <v>255.084</v>
       </c>
       <c r="F45">
-        <v>355.223</v>
+        <v>363.484</v>
       </c>
       <c r="G45">
         <v>213.5</v>
@@ -4965,28 +4965,28 @@
         <v>43.5</v>
       </c>
       <c r="M45">
-        <v>52.14673640000001</v>
+        <v>53.35945120000001</v>
       </c>
       <c r="N45">
-        <v>-8.646736400000009</v>
+        <v>-9.859451200000009</v>
       </c>
       <c r="O45">
         <v>-0</v>
       </c>
       <c r="P45">
-        <v>-8.646736400000009</v>
+        <v>-9.859451200000009</v>
       </c>
       <c r="Q45">
-        <v>9.353263599999991</v>
+        <v>8.140548799999991</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1243159798287293</v>
+        <v>0.1257180508970995</v>
       </c>
       <c r="T45">
-        <v>1.530422588578338</v>
+        <v>1.55775156337438</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8341845147570921</v>
+        <v>0.8152257757853401</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1349941085023758</v>
+        <v>0.1603041085023758</v>
       </c>
       <c r="C46">
-        <v>171.3066758538943</v>
+        <v>92.02755159424515</v>
       </c>
       <c r="D46">
-        <v>321.2906758538942</v>
+        <v>250.2725515942452</v>
       </c>
       <c r="E46">
-        <v>255.084</v>
+        <v>263.345</v>
       </c>
       <c r="F46">
-        <v>363.484</v>
+        <v>371.745</v>
       </c>
       <c r="G46">
         <v>213.5</v>
@@ -5047,45 +5047,45 @@
         <v>43.5</v>
       </c>
       <c r="M46">
-        <v>53.35945120000001</v>
+        <v>74.64639600000001</v>
       </c>
       <c r="N46">
-        <v>-9.859451200000009</v>
+        <v>-31.14639600000001</v>
       </c>
       <c r="O46">
         <v>-0</v>
       </c>
       <c r="P46">
-        <v>-9.859451200000009</v>
+        <v>-31.14639600000001</v>
       </c>
       <c r="Q46">
-        <v>8.140548799999991</v>
+        <v>-13.14639600000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1257180508970995</v>
+        <v>0.1271711063679559</v>
       </c>
       <c r="T46">
-        <v>1.55775156337438</v>
+        <v>1.586074319072096</v>
       </c>
       <c r="U46">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V46">
         <v>0</v>
       </c>
       <c r="W46">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.8152257757853401</v>
+        <v>0.5827474912519554</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1603041085023758</v>
+        <v>0.1618541085023757</v>
       </c>
       <c r="C47">
-        <v>92.02755159424515</v>
+        <v>80.4239516641174</v>
       </c>
       <c r="D47">
-        <v>250.2725515942452</v>
+        <v>246.9299516641174</v>
       </c>
       <c r="E47">
-        <v>263.345</v>
+        <v>271.606</v>
       </c>
       <c r="F47">
-        <v>371.745</v>
+        <v>380.006</v>
       </c>
       <c r="G47">
         <v>213.5</v>
@@ -5129,28 +5129,28 @@
         <v>43.5</v>
       </c>
       <c r="M47">
-        <v>74.64639600000001</v>
+        <v>76.30520480000001</v>
       </c>
       <c r="N47">
-        <v>-31.14639600000001</v>
+        <v>-32.80520480000001</v>
       </c>
       <c r="O47">
         <v>-0</v>
       </c>
       <c r="P47">
-        <v>-31.14639600000001</v>
+        <v>-32.80520480000001</v>
       </c>
       <c r="Q47">
-        <v>-13.14639600000001</v>
+        <v>-14.80520480000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1271711063679559</v>
+        <v>0.1286779787081032</v>
       </c>
       <c r="T47">
-        <v>1.586074319072096</v>
+        <v>1.615446065721579</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5827474912519554</v>
+        <v>0.5700790675290868</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1618541085023757</v>
+        <v>0.1634041085023757</v>
       </c>
       <c r="C48">
-        <v>80.4239516641174</v>
+        <v>68.90846140902863</v>
       </c>
       <c r="D48">
-        <v>246.9299516641174</v>
+        <v>243.6754614090287</v>
       </c>
       <c r="E48">
-        <v>271.606</v>
+        <v>279.8670000000001</v>
       </c>
       <c r="F48">
-        <v>380.006</v>
+        <v>388.2670000000001</v>
       </c>
       <c r="G48">
         <v>213.5</v>
@@ -5211,28 +5211,28 @@
         <v>43.5</v>
       </c>
       <c r="M48">
-        <v>76.30520480000001</v>
+        <v>77.96401360000002</v>
       </c>
       <c r="N48">
-        <v>-32.80520480000001</v>
+        <v>-34.46401360000002</v>
       </c>
       <c r="O48">
         <v>-0</v>
       </c>
       <c r="P48">
-        <v>-32.80520480000001</v>
+        <v>-34.46401360000002</v>
       </c>
       <c r="Q48">
-        <v>-14.80520480000001</v>
+        <v>-16.46401360000002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1286779787081032</v>
+        <v>0.1302417141554259</v>
       </c>
       <c r="T48">
-        <v>1.615446065721579</v>
+        <v>1.645926180169156</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5700790675290868</v>
+        <v>0.5579497256667657</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1634041085023757</v>
+        <v>0.1649541085023757</v>
       </c>
       <c r="C49">
-        <v>68.90846140902863</v>
+        <v>57.47764234083877</v>
       </c>
       <c r="D49">
-        <v>243.6754614090287</v>
+        <v>240.5056423408388</v>
       </c>
       <c r="E49">
-        <v>279.8670000000001</v>
+        <v>288.128</v>
       </c>
       <c r="F49">
-        <v>388.2670000000001</v>
+        <v>396.528</v>
       </c>
       <c r="G49">
         <v>213.5</v>
@@ -5293,28 +5293,28 @@
         <v>43.5</v>
       </c>
       <c r="M49">
-        <v>77.96401360000002</v>
+        <v>79.6228224</v>
       </c>
       <c r="N49">
-        <v>-34.46401360000002</v>
+        <v>-36.1228224</v>
       </c>
       <c r="O49">
         <v>-0</v>
       </c>
       <c r="P49">
-        <v>-34.46401360000002</v>
+        <v>-36.1228224</v>
       </c>
       <c r="Q49">
-        <v>-16.46401360000002</v>
+        <v>-18.1228224</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1302417141554259</v>
+        <v>0.1318655932737995</v>
       </c>
       <c r="T49">
-        <v>1.645926180169156</v>
+        <v>1.677578606710871</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5579497256667657</v>
+        <v>0.5463257730487081</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1649541085023757</v>
+        <v>0.1665041085023757</v>
       </c>
       <c r="C50">
-        <v>57.47764234083877</v>
+        <v>46.12823259030438</v>
       </c>
       <c r="D50">
-        <v>240.5056423408388</v>
+        <v>237.4172325903044</v>
       </c>
       <c r="E50">
-        <v>288.128</v>
+        <v>296.389</v>
       </c>
       <c r="F50">
-        <v>396.528</v>
+        <v>404.789</v>
       </c>
       <c r="G50">
         <v>213.5</v>
@@ -5375,28 +5375,28 @@
         <v>43.5</v>
       </c>
       <c r="M50">
-        <v>79.6228224</v>
+        <v>81.28163120000001</v>
       </c>
       <c r="N50">
-        <v>-36.1228224</v>
+        <v>-37.78163120000001</v>
       </c>
       <c r="O50">
         <v>-0</v>
       </c>
       <c r="P50">
-        <v>-36.1228224</v>
+        <v>-37.78163120000001</v>
       </c>
       <c r="Q50">
-        <v>-18.1228224</v>
+        <v>-19.78163120000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1318655932737995</v>
+        <v>0.1335531539262269</v>
       </c>
       <c r="T50">
-        <v>1.677578606710871</v>
+        <v>1.710472304881672</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5463257730487081</v>
+        <v>0.5351762674762855</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1665041085023757</v>
+        <v>0.1680541085023757</v>
       </c>
       <c r="C51">
-        <v>46.12823259030438</v>
+        <v>34.85713571075604</v>
       </c>
       <c r="D51">
-        <v>237.4172325903044</v>
+        <v>234.4071357107561</v>
       </c>
       <c r="E51">
-        <v>296.389</v>
+        <v>304.65</v>
       </c>
       <c r="F51">
-        <v>404.789</v>
+        <v>413.05</v>
       </c>
       <c r="G51">
         <v>213.5</v>
@@ -5457,28 +5457,28 @@
         <v>43.5</v>
       </c>
       <c r="M51">
-        <v>81.28163120000001</v>
+        <v>82.94044000000001</v>
       </c>
       <c r="N51">
-        <v>-37.78163120000001</v>
+        <v>-39.44044000000001</v>
       </c>
       <c r="O51">
         <v>-0</v>
       </c>
       <c r="P51">
-        <v>-37.78163120000001</v>
+        <v>-39.44044000000001</v>
       </c>
       <c r="Q51">
-        <v>-19.78163120000001</v>
+        <v>-21.44044000000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1335531539262269</v>
+        <v>0.1353082170047515</v>
       </c>
       <c r="T51">
-        <v>1.710472304881672</v>
+        <v>1.744681750979306</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5351762674762855</v>
+        <v>0.5244727421267599</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1680541085023757</v>
+        <v>0.1696041085023757</v>
       </c>
       <c r="C52">
-        <v>34.85713571075604</v>
+        <v>23.66141032282837</v>
       </c>
       <c r="D52">
-        <v>234.4071357107561</v>
+        <v>231.4724103228284</v>
       </c>
       <c r="E52">
-        <v>304.65</v>
+        <v>312.9110000000001</v>
       </c>
       <c r="F52">
-        <v>413.05</v>
+        <v>421.311</v>
       </c>
       <c r="G52">
         <v>213.5</v>
@@ -5539,28 +5539,28 @@
         <v>43.5</v>
       </c>
       <c r="M52">
-        <v>82.94044000000001</v>
+        <v>84.59924880000001</v>
       </c>
       <c r="N52">
-        <v>-39.44044000000001</v>
+        <v>-41.09924880000001</v>
       </c>
       <c r="O52">
         <v>-0</v>
       </c>
       <c r="P52">
-        <v>-39.44044000000001</v>
+        <v>-41.09924880000001</v>
       </c>
       <c r="Q52">
-        <v>-21.44044000000001</v>
+        <v>-23.09924880000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1353082170047515</v>
+        <v>0.1371349153109709</v>
       </c>
       <c r="T52">
-        <v>1.744681750979306</v>
+        <v>1.780287500999292</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5244727421267599</v>
+        <v>0.5141889628693723</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1696041085023757</v>
+        <v>0.1711541085023757</v>
       </c>
       <c r="C53">
-        <v>23.66141032282837</v>
+        <v>12.53826052744625</v>
       </c>
       <c r="D53">
-        <v>231.4724103228284</v>
+        <v>228.6102605274463</v>
       </c>
       <c r="E53">
-        <v>312.9110000000001</v>
+        <v>321.172</v>
       </c>
       <c r="F53">
-        <v>421.311</v>
+        <v>429.572</v>
       </c>
       <c r="G53">
         <v>213.5</v>
@@ -5621,28 +5621,28 @@
         <v>43.5</v>
       </c>
       <c r="M53">
-        <v>84.59924880000001</v>
+        <v>86.2580576</v>
       </c>
       <c r="N53">
-        <v>-41.09924880000001</v>
+        <v>-42.7580576</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-41.09924880000001</v>
+        <v>-42.7580576</v>
       </c>
       <c r="Q53">
-        <v>-23.09924880000001</v>
+        <v>-24.7580576</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1371349153109709</v>
+        <v>0.1390377260466161</v>
       </c>
       <c r="T53">
-        <v>1.780287500999292</v>
+        <v>1.817376823936777</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5141889628693723</v>
+        <v>0.504300713583423</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1711541085023757</v>
+        <v>0.1912541085023757</v>
       </c>
       <c r="C54">
-        <v>12.53826052744625</v>
+        <v>-27.31391475053925</v>
       </c>
       <c r="D54">
-        <v>228.6102605274463</v>
+        <v>197.0190852494608</v>
       </c>
       <c r="E54">
-        <v>321.172</v>
+        <v>329.433</v>
       </c>
       <c r="F54">
-        <v>429.572</v>
+        <v>437.833</v>
       </c>
       <c r="G54">
         <v>213.5</v>
@@ -5703,45 +5703,45 @@
         <v>43.5</v>
       </c>
       <c r="M54">
-        <v>86.2580576</v>
+        <v>103.2410214</v>
       </c>
       <c r="N54">
-        <v>-42.7580576</v>
+        <v>-59.74102140000001</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-42.7580576</v>
+        <v>-59.74102140000001</v>
       </c>
       <c r="Q54">
-        <v>-24.7580576</v>
+        <v>-41.74102140000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1390377260466161</v>
+        <v>0.1410215074518633</v>
       </c>
       <c r="T54">
-        <v>1.817376823936777</v>
+        <v>1.856044415935432</v>
       </c>
       <c r="U54">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V54">
         <v>0</v>
       </c>
       <c r="W54">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.504300713583423</v>
+        <v>0.4213441460585937</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1912541085023757</v>
+        <v>0.1931541085023757</v>
       </c>
       <c r="C55">
-        <v>-27.31391475053925</v>
+        <v>-38.11530039555805</v>
       </c>
       <c r="D55">
-        <v>197.0190852494608</v>
+        <v>194.478699604442</v>
       </c>
       <c r="E55">
-        <v>329.433</v>
+        <v>337.6940000000001</v>
       </c>
       <c r="F55">
-        <v>437.833</v>
+        <v>446.0940000000001</v>
       </c>
       <c r="G55">
         <v>213.5</v>
@@ -5785,28 +5785,28 @@
         <v>43.5</v>
       </c>
       <c r="M55">
-        <v>103.2410214</v>
+        <v>105.1889652</v>
       </c>
       <c r="N55">
-        <v>-59.74102140000001</v>
+        <v>-61.68896520000001</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-59.74102140000001</v>
+        <v>-61.68896520000001</v>
       </c>
       <c r="Q55">
-        <v>-41.74102140000001</v>
+        <v>-43.68896520000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1410215074518633</v>
+        <v>0.1430915402225559</v>
       </c>
       <c r="T55">
-        <v>1.856044415935432</v>
+        <v>1.896393207586202</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4213441460585937</v>
+        <v>0.4135414766871383</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1931541085023757</v>
+        <v>0.1950541085023758</v>
       </c>
       <c r="C56">
-        <v>-38.11530039555805</v>
+        <v>-48.85200798549397</v>
       </c>
       <c r="D56">
-        <v>194.478699604442</v>
+        <v>192.0029920145061</v>
       </c>
       <c r="E56">
-        <v>337.6940000000001</v>
+        <v>345.955</v>
       </c>
       <c r="F56">
-        <v>446.0940000000001</v>
+        <v>454.3550000000001</v>
       </c>
       <c r="G56">
         <v>213.5</v>
@@ -5867,28 +5867,28 @@
         <v>43.5</v>
       </c>
       <c r="M56">
-        <v>105.1889652</v>
+        <v>107.136909</v>
       </c>
       <c r="N56">
-        <v>-61.68896520000001</v>
+        <v>-63.63690900000002</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-61.68896520000001</v>
+        <v>-63.63690900000002</v>
       </c>
       <c r="Q56">
-        <v>-43.68896520000001</v>
+        <v>-45.63690900000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1430915402225559</v>
+        <v>0.1452535744497238</v>
       </c>
       <c r="T56">
-        <v>1.896393207586202</v>
+        <v>1.938535278865895</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4135414766871383</v>
+        <v>0.4060225407473721</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1950541085023758</v>
+        <v>0.1969541085023758</v>
       </c>
       <c r="C57">
-        <v>-48.85200798549397</v>
+        <v>-59.52647652063359</v>
       </c>
       <c r="D57">
-        <v>192.0029920145061</v>
+        <v>189.5895234793665</v>
       </c>
       <c r="E57">
-        <v>345.955</v>
+        <v>354.216</v>
       </c>
       <c r="F57">
-        <v>454.3550000000001</v>
+        <v>462.616</v>
       </c>
       <c r="G57">
         <v>213.5</v>
@@ -5949,28 +5949,28 @@
         <v>43.5</v>
       </c>
       <c r="M57">
-        <v>107.136909</v>
+        <v>109.0848528</v>
       </c>
       <c r="N57">
-        <v>-63.63690900000002</v>
+        <v>-65.58485280000002</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-63.63690900000002</v>
+        <v>-65.58485280000002</v>
       </c>
       <c r="Q57">
-        <v>-45.63690900000002</v>
+        <v>-47.58485280000002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1452535744497238</v>
+        <v>0.1475138829599449</v>
       </c>
       <c r="T57">
-        <v>1.938535278865895</v>
+        <v>1.98259289884012</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4060225407473721</v>
+        <v>0.3987721382340261</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1969541085023758</v>
+        <v>0.1988541085023758</v>
       </c>
       <c r="C58">
-        <v>-59.52647652063359</v>
+        <v>-70.14102389113884</v>
       </c>
       <c r="D58">
-        <v>189.5895234793665</v>
+        <v>187.2359761088612</v>
       </c>
       <c r="E58">
-        <v>354.216</v>
+        <v>362.4770000000001</v>
       </c>
       <c r="F58">
-        <v>462.616</v>
+        <v>470.8770000000001</v>
       </c>
       <c r="G58">
         <v>213.5</v>
@@ -6031,28 +6031,28 @@
         <v>43.5</v>
       </c>
       <c r="M58">
-        <v>109.0848528</v>
+        <v>111.0327966</v>
       </c>
       <c r="N58">
-        <v>-65.58485280000002</v>
+        <v>-67.53279660000003</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-65.58485280000002</v>
+        <v>-67.53279660000003</v>
       </c>
       <c r="Q58">
-        <v>-47.58485280000002</v>
+        <v>-49.53279660000003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1475138829599449</v>
+        <v>0.1498793220985482</v>
       </c>
       <c r="T58">
-        <v>1.98259289884012</v>
+        <v>2.028699710441054</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3987721382340261</v>
+        <v>0.3917761358088677</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1988541085023758</v>
+        <v>0.2007541085023757</v>
       </c>
       <c r="C59">
-        <v>-70.14102389113884</v>
+        <v>-80.69785430212391</v>
       </c>
       <c r="D59">
-        <v>187.2359761088612</v>
+        <v>184.9401456978762</v>
       </c>
       <c r="E59">
-        <v>362.4770000000001</v>
+        <v>370.7380000000001</v>
       </c>
       <c r="F59">
-        <v>470.8770000000001</v>
+        <v>479.1380000000001</v>
       </c>
       <c r="G59">
         <v>213.5</v>
@@ -6113,28 +6113,28 @@
         <v>43.5</v>
       </c>
       <c r="M59">
-        <v>111.0327966</v>
+        <v>112.9807404</v>
       </c>
       <c r="N59">
-        <v>-67.53279660000003</v>
+        <v>-69.48074040000003</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-67.53279660000003</v>
+        <v>-69.48074040000003</v>
       </c>
       <c r="Q59">
-        <v>-49.53279660000003</v>
+        <v>-51.48074040000003</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1498793220985482</v>
+        <v>0.1523574011961327</v>
       </c>
       <c r="T59">
-        <v>2.028699710441054</v>
+        <v>2.077002084499174</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3917761358088677</v>
+        <v>0.3850213748466459</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2007541085023757</v>
+        <v>0.2026541085023757</v>
       </c>
       <c r="C60">
-        <v>-80.6978543021238</v>
+        <v>-91.1990651590848</v>
       </c>
       <c r="D60">
-        <v>184.9401456978762</v>
+        <v>182.6999348409152</v>
       </c>
       <c r="E60">
-        <v>370.7379999999999</v>
+        <v>378.999</v>
       </c>
       <c r="F60">
-        <v>479.138</v>
+        <v>487.399</v>
       </c>
       <c r="G60">
         <v>213.5</v>
@@ -6195,28 +6195,28 @@
         <v>43.5</v>
       </c>
       <c r="M60">
-        <v>112.9807404</v>
+        <v>114.9286842</v>
       </c>
       <c r="N60">
-        <v>-69.4807404</v>
+        <v>-71.42868420000001</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-69.4807404</v>
+        <v>-71.42868420000001</v>
       </c>
       <c r="Q60">
-        <v>-51.4807404</v>
+        <v>-53.42868420000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1523574011961327</v>
+        <v>0.1549563622009164</v>
       </c>
       <c r="T60">
-        <v>2.077002084499173</v>
+        <v>2.127660671925982</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.385021374846646</v>
+        <v>0.3784955888322961</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2026541085023757</v>
+        <v>0.2045541085023757</v>
       </c>
       <c r="C61">
-        <v>-91.1990651590848</v>
+        <v>-101.6466534588927</v>
       </c>
       <c r="D61">
-        <v>182.6999348409152</v>
+        <v>180.5133465411072</v>
       </c>
       <c r="E61">
-        <v>378.999</v>
+        <v>387.26</v>
       </c>
       <c r="F61">
-        <v>487.399</v>
+        <v>495.66</v>
       </c>
       <c r="G61">
         <v>213.5</v>
@@ -6277,28 +6277,28 @@
         <v>43.5</v>
       </c>
       <c r="M61">
-        <v>114.9286842</v>
+        <v>116.876628</v>
       </c>
       <c r="N61">
-        <v>-71.42868420000001</v>
+        <v>-73.376628</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-71.42868420000001</v>
+        <v>-73.376628</v>
       </c>
       <c r="Q61">
-        <v>-53.42868420000001</v>
+        <v>-55.376628</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1549563622009164</v>
+        <v>0.1576852712559393</v>
       </c>
       <c r="T61">
-        <v>2.127660671925982</v>
+        <v>2.180852188724132</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3784955888322961</v>
+        <v>0.3721873290184244</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2045541085023757</v>
+        <v>0.2064541085023757</v>
       </c>
       <c r="C62">
-        <v>-101.6466534588927</v>
+        <v>-112.0425217272822</v>
       </c>
       <c r="D62">
-        <v>180.5133465411072</v>
+        <v>178.3784782727178</v>
       </c>
       <c r="E62">
-        <v>387.26</v>
+        <v>395.521</v>
       </c>
       <c r="F62">
-        <v>495.66</v>
+        <v>503.921</v>
       </c>
       <c r="G62">
         <v>213.5</v>
@@ -6359,28 +6359,28 @@
         <v>43.5</v>
       </c>
       <c r="M62">
-        <v>116.876628</v>
+        <v>118.8245718</v>
       </c>
       <c r="N62">
-        <v>-73.376628</v>
+        <v>-75.3245718</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-73.376628</v>
+        <v>-75.3245718</v>
       </c>
       <c r="Q62">
-        <v>-55.376628</v>
+        <v>-57.3245718</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1576852712559393</v>
+        <v>0.160554124365066</v>
       </c>
       <c r="T62">
-        <v>2.180852188724132</v>
+        <v>2.236771475614495</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3721873290184244</v>
+        <v>0.3660858973951716</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2064541085023757</v>
+        <v>0.2083541085023757</v>
       </c>
       <c r="C63">
-        <v>-112.0425217272822</v>
+        <v>-122.3884835399405</v>
       </c>
       <c r="D63">
-        <v>178.3784782727178</v>
+        <v>176.2935164600595</v>
       </c>
       <c r="E63">
-        <v>395.521</v>
+        <v>403.782</v>
       </c>
       <c r="F63">
-        <v>503.921</v>
+        <v>512.182</v>
       </c>
       <c r="G63">
         <v>213.5</v>
@@ -6441,28 +6441,28 @@
         <v>43.5</v>
       </c>
       <c r="M63">
-        <v>118.8245718</v>
+        <v>120.7725156</v>
       </c>
       <c r="N63">
-        <v>-75.3245718</v>
+        <v>-77.27251560000001</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-75.3245718</v>
+        <v>-77.27251560000001</v>
       </c>
       <c r="Q63">
-        <v>-57.3245718</v>
+        <v>-59.27251560000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.160554124365066</v>
+        <v>0.163573969743094</v>
       </c>
       <c r="T63">
-        <v>2.236771475614495</v>
+        <v>2.295633882867508</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3660858973951716</v>
+        <v>0.3601812861468624</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2083541085023757</v>
+        <v>0.2102541085023757</v>
       </c>
       <c r="C64">
-        <v>-122.3884835399405</v>
+        <v>-132.6862686608745</v>
       </c>
       <c r="D64">
-        <v>176.2935164600595</v>
+        <v>174.2567313391255</v>
       </c>
       <c r="E64">
-        <v>403.782</v>
+        <v>412.043</v>
       </c>
       <c r="F64">
-        <v>512.182</v>
+        <v>520.443</v>
       </c>
       <c r="G64">
         <v>213.5</v>
@@ -6523,28 +6523,28 @@
         <v>43.5</v>
       </c>
       <c r="M64">
-        <v>120.7725156</v>
+        <v>122.7204594</v>
       </c>
       <c r="N64">
-        <v>-77.27251560000001</v>
+        <v>-79.2204594</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-77.27251560000001</v>
+        <v>-79.2204594</v>
       </c>
       <c r="Q64">
-        <v>-59.27251560000001</v>
+        <v>-61.2204594</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.163573969743094</v>
+        <v>0.1667570500064209</v>
       </c>
       <c r="T64">
-        <v>2.295633882867508</v>
+        <v>2.357678041863926</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3601812861468624</v>
+        <v>0.35446412287469</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2102541085023757</v>
+        <v>0.2121541085023757</v>
       </c>
       <c r="C65">
-        <v>-132.6862686608745</v>
+        <v>-142.9375278286523</v>
       </c>
       <c r="D65">
-        <v>174.2567313391255</v>
+        <v>172.2664721713478</v>
       </c>
       <c r="E65">
-        <v>412.043</v>
+        <v>420.3040000000001</v>
       </c>
       <c r="F65">
-        <v>520.443</v>
+        <v>528.7040000000001</v>
       </c>
       <c r="G65">
         <v>213.5</v>
@@ -6605,28 +6605,28 @@
         <v>43.5</v>
       </c>
       <c r="M65">
-        <v>122.7204594</v>
+        <v>124.6684032</v>
       </c>
       <c r="N65">
-        <v>-79.2204594</v>
+        <v>-81.16840320000001</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-79.2204594</v>
+        <v>-81.16840320000001</v>
       </c>
       <c r="Q65">
-        <v>-61.2204594</v>
+        <v>-63.16840320000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1667570500064209</v>
+        <v>0.1701169680621548</v>
       </c>
       <c r="T65">
-        <v>2.357678041863926</v>
+        <v>2.423169098582369</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.35446412287469</v>
+        <v>0.3489256209547729</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2121541085023757</v>
+        <v>0.2140541085023757</v>
       </c>
       <c r="C66">
-        <v>-142.9375278286523</v>
+        <v>-153.143837218354</v>
       </c>
       <c r="D66">
-        <v>172.2664721713478</v>
+        <v>170.3211627816461</v>
       </c>
       <c r="E66">
-        <v>420.3040000000001</v>
+        <v>428.5650000000001</v>
       </c>
       <c r="F66">
-        <v>528.7040000000001</v>
+        <v>536.965</v>
       </c>
       <c r="G66">
         <v>213.5</v>
@@ -6687,28 +6687,28 @@
         <v>43.5</v>
       </c>
       <c r="M66">
-        <v>124.6684032</v>
+        <v>126.616347</v>
       </c>
       <c r="N66">
-        <v>-81.16840320000001</v>
+        <v>-83.11634700000002</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-81.16840320000001</v>
+        <v>-83.11634700000002</v>
       </c>
       <c r="Q66">
-        <v>-63.16840320000001</v>
+        <v>-65.11634700000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1701169680621548</v>
+        <v>0.1736688814353592</v>
       </c>
       <c r="T66">
-        <v>2.423169098582369</v>
+        <v>2.492402501399009</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3489256209547729</v>
+        <v>0.3435575344785456</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2140541085023757</v>
+        <v>0.2159541085023757</v>
       </c>
       <c r="C67">
-        <v>-153.143837218354</v>
+        <v>-163.3067026045817</v>
       </c>
       <c r="D67">
-        <v>170.3211627816461</v>
+        <v>168.4192973954183</v>
       </c>
       <c r="E67">
-        <v>428.5650000000001</v>
+        <v>436.826</v>
       </c>
       <c r="F67">
-        <v>536.965</v>
+        <v>545.226</v>
       </c>
       <c r="G67">
         <v>213.5</v>
@@ -6769,28 +6769,28 @@
         <v>43.5</v>
       </c>
       <c r="M67">
-        <v>126.616347</v>
+        <v>128.5642908</v>
       </c>
       <c r="N67">
-        <v>-83.11634700000002</v>
+        <v>-85.06429080000001</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-83.11634700000002</v>
+        <v>-85.06429080000001</v>
       </c>
       <c r="Q67">
-        <v>-65.11634700000002</v>
+        <v>-67.06429080000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1736688814353592</v>
+        <v>0.1774297308893404</v>
       </c>
       <c r="T67">
-        <v>2.492402501399009</v>
+        <v>2.565708457322509</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3435575344785456</v>
+        <v>0.3383521172894768</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2159541085023757</v>
+        <v>0.2178541085023757</v>
       </c>
       <c r="C68">
-        <v>-163.3067026045817</v>
+        <v>-173.4275632486355</v>
       </c>
       <c r="D68">
-        <v>168.4192973954183</v>
+        <v>166.5594367513646</v>
       </c>
       <c r="E68">
-        <v>436.826</v>
+        <v>445.0870000000001</v>
       </c>
       <c r="F68">
-        <v>545.226</v>
+        <v>553.4870000000001</v>
       </c>
       <c r="G68">
         <v>213.5</v>
@@ -6851,28 +6851,28 @@
         <v>43.5</v>
       </c>
       <c r="M68">
-        <v>128.5642908</v>
+        <v>130.5122346</v>
       </c>
       <c r="N68">
-        <v>-85.06429080000001</v>
+        <v>-87.01223460000003</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-85.06429080000001</v>
+        <v>-87.01223460000003</v>
       </c>
       <c r="Q68">
-        <v>-67.06429080000001</v>
+        <v>-69.01223460000003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1774297308893404</v>
+        <v>0.1814185106132598</v>
       </c>
       <c r="T68">
-        <v>2.565708457322509</v>
+        <v>2.643457198453494</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3383521172894768</v>
+        <v>0.3333020856881412</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2178541085023757</v>
+        <v>0.2197541085023758</v>
       </c>
       <c r="C69">
-        <v>-173.4275632486355</v>
+        <v>-183.5077955309432</v>
       </c>
       <c r="D69">
-        <v>166.5594367513646</v>
+        <v>164.7402044690569</v>
       </c>
       <c r="E69">
-        <v>445.0870000000001</v>
+        <v>453.3480000000001</v>
       </c>
       <c r="F69">
-        <v>553.4870000000001</v>
+        <v>561.748</v>
       </c>
       <c r="G69">
         <v>213.5</v>
@@ -6933,28 +6933,28 @@
         <v>43.5</v>
       </c>
       <c r="M69">
-        <v>130.5122346</v>
+        <v>132.4601784</v>
       </c>
       <c r="N69">
-        <v>-87.01223460000003</v>
+        <v>-88.96017840000002</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-87.01223460000003</v>
+        <v>-88.96017840000002</v>
       </c>
       <c r="Q69">
-        <v>-69.01223460000003</v>
+        <v>-70.96017840000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1814185106132598</v>
+        <v>0.1856565890699242</v>
       </c>
       <c r="T69">
-        <v>2.643457198453494</v>
+        <v>2.726065235905166</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3333020856881412</v>
+        <v>0.3284005844280216</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2197541085023758</v>
+        <v>0.2216541085023757</v>
       </c>
       <c r="C70">
-        <v>-183.5077955309432</v>
+        <v>-193.5487163480162</v>
       </c>
       <c r="D70">
-        <v>164.7402044690569</v>
+        <v>162.9602836519838</v>
       </c>
       <c r="E70">
-        <v>453.3480000000001</v>
+        <v>461.609</v>
       </c>
       <c r="F70">
-        <v>561.748</v>
+        <v>570.009</v>
       </c>
       <c r="G70">
         <v>213.5</v>
@@ -7015,28 +7015,28 @@
         <v>43.5</v>
       </c>
       <c r="M70">
-        <v>132.4601784</v>
+        <v>134.4081222</v>
       </c>
       <c r="N70">
-        <v>-88.96017840000002</v>
+        <v>-90.90812220000001</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-88.96017840000002</v>
+        <v>-90.90812220000001</v>
       </c>
       <c r="Q70">
-        <v>-70.96017840000002</v>
+        <v>-72.90812220000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1856565890699242</v>
+        <v>0.1901680919431475</v>
       </c>
       <c r="T70">
-        <v>2.726065235905166</v>
+        <v>2.814002824160171</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3284005844280216</v>
+        <v>0.3236411556681952</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2216541085023757</v>
+        <v>0.2235541085023757</v>
       </c>
       <c r="C71">
-        <v>-193.5487163480162</v>
+        <v>-203.5515862915436</v>
       </c>
       <c r="D71">
-        <v>162.9602836519838</v>
+        <v>161.2184137084566</v>
       </c>
       <c r="E71">
-        <v>461.609</v>
+        <v>469.8700000000001</v>
       </c>
       <c r="F71">
-        <v>570.009</v>
+        <v>578.2700000000001</v>
       </c>
       <c r="G71">
         <v>213.5</v>
@@ -7097,28 +7097,28 @@
         <v>43.5</v>
       </c>
       <c r="M71">
-        <v>134.4081222</v>
+        <v>136.356066</v>
       </c>
       <c r="N71">
-        <v>-90.90812220000001</v>
+        <v>-92.85606600000003</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-90.90812220000001</v>
+        <v>-92.85606600000003</v>
       </c>
       <c r="Q71">
-        <v>-72.90812220000001</v>
+        <v>-74.85606600000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1901680919431475</v>
+        <v>0.1949803616745858</v>
       </c>
       <c r="T71">
-        <v>2.814002824160171</v>
+        <v>2.907802918298843</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3236411556681952</v>
+        <v>0.3190177105872209</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2235541085023757</v>
+        <v>0.2254541085023757</v>
       </c>
       <c r="C72">
-        <v>-203.5515862915436</v>
+        <v>-213.5176126257563</v>
       </c>
       <c r="D72">
-        <v>161.2184137084566</v>
+        <v>159.5133873742438</v>
       </c>
       <c r="E72">
-        <v>469.8700000000001</v>
+        <v>478.1310000000001</v>
       </c>
       <c r="F72">
-        <v>578.2700000000001</v>
+        <v>586.5310000000001</v>
       </c>
       <c r="G72">
         <v>213.5</v>
@@ -7179,28 +7179,28 @@
         <v>43.5</v>
       </c>
       <c r="M72">
-        <v>136.356066</v>
+        <v>138.3040098</v>
       </c>
       <c r="N72">
-        <v>-92.85606600000003</v>
+        <v>-94.80400980000002</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-92.85606600000003</v>
+        <v>-94.80400980000002</v>
       </c>
       <c r="Q72">
-        <v>-74.85606600000003</v>
+        <v>-76.80400980000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1949803616745858</v>
+        <v>0.2001245120771578</v>
       </c>
       <c r="T72">
-        <v>2.907802918298843</v>
+        <v>3.00807198444708</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3190177105872209</v>
+        <v>0.3145245033958516</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2254541085023757</v>
+        <v>0.2273541085023758</v>
       </c>
       <c r="C73">
-        <v>-213.5176126257562</v>
+        <v>-223.4479520778409</v>
       </c>
       <c r="D73">
-        <v>159.5133873742438</v>
+        <v>157.8440479221591</v>
       </c>
       <c r="E73">
-        <v>478.131</v>
+        <v>486.3920000000001</v>
       </c>
       <c r="F73">
-        <v>586.5309999999999</v>
+        <v>594.792</v>
       </c>
       <c r="G73">
         <v>213.5</v>
@@ -7261,28 +7261,28 @@
         <v>43.5</v>
       </c>
       <c r="M73">
-        <v>138.3040098</v>
+        <v>140.2519536</v>
       </c>
       <c r="N73">
-        <v>-94.80400979999999</v>
+        <v>-96.75195360000001</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-94.80400979999999</v>
+        <v>-96.75195360000001</v>
       </c>
       <c r="Q73">
-        <v>-76.80400979999999</v>
+        <v>-78.75195360000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2001245120771577</v>
+        <v>0.205636101794199</v>
       </c>
       <c r="T73">
-        <v>3.008071984447079</v>
+        <v>3.11550312674876</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3145245033958517</v>
+        <v>0.3101561075153537</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2273541085023758</v>
+        <v>0.2292541085023757</v>
       </c>
       <c r="C74">
-        <v>-223.4479520778409</v>
+        <v>-233.3437134549523</v>
       </c>
       <c r="D74">
-        <v>157.8440479221591</v>
+        <v>156.2092865450477</v>
       </c>
       <c r="E74">
-        <v>486.3920000000001</v>
+        <v>494.653</v>
       </c>
       <c r="F74">
-        <v>594.792</v>
+        <v>603.053</v>
       </c>
       <c r="G74">
         <v>213.5</v>
@@ -7343,28 +7343,28 @@
         <v>43.5</v>
       </c>
       <c r="M74">
-        <v>140.2519536</v>
+        <v>142.1998974</v>
       </c>
       <c r="N74">
-        <v>-96.75195360000001</v>
+        <v>-98.6998974</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-96.75195360000001</v>
+        <v>-98.6998974</v>
       </c>
       <c r="Q74">
-        <v>-78.75195360000001</v>
+        <v>-80.6998974</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.205636101794199</v>
+        <v>0.2115559574162064</v>
       </c>
       <c r="T74">
-        <v>3.11550312674876</v>
+        <v>3.230892131443158</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3101561075153537</v>
+        <v>0.3059073937137735</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2292541085023757</v>
+        <v>0.2311541085023757</v>
       </c>
       <c r="C75">
-        <v>-233.3437134549523</v>
+        <v>-243.2059601002717</v>
       </c>
       <c r="D75">
-        <v>156.2092865450477</v>
+        <v>154.6080398997283</v>
       </c>
       <c r="E75">
-        <v>494.653</v>
+        <v>502.914</v>
       </c>
       <c r="F75">
-        <v>603.053</v>
+        <v>611.314</v>
       </c>
       <c r="G75">
         <v>213.5</v>
@@ -7425,28 +7425,28 @@
         <v>43.5</v>
       </c>
       <c r="M75">
-        <v>142.1998974</v>
+        <v>144.1478412</v>
       </c>
       <c r="N75">
-        <v>-98.6998974</v>
+        <v>-100.6478412</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-98.6998974</v>
+        <v>-100.6478412</v>
       </c>
       <c r="Q75">
-        <v>-80.6998974</v>
+        <v>-82.64784119999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2115559574162064</v>
+        <v>0.217931186547599</v>
       </c>
       <c r="T75">
-        <v>3.230892131443158</v>
+        <v>3.355157213421742</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3059073937137735</v>
+        <v>0.3017735100149388</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2311541085023757</v>
+        <v>0.2330541085023757</v>
       </c>
       <c r="C76">
-        <v>-243.2059601002717</v>
+        <v>-253.0357121995388</v>
       </c>
       <c r="D76">
-        <v>154.6080398997283</v>
+        <v>153.0392878004613</v>
       </c>
       <c r="E76">
-        <v>502.914</v>
+        <v>511.1750000000001</v>
       </c>
       <c r="F76">
-        <v>611.314</v>
+        <v>619.575</v>
       </c>
       <c r="G76">
         <v>213.5</v>
@@ -7507,28 +7507,28 @@
         <v>43.5</v>
       </c>
       <c r="M76">
-        <v>144.1478412</v>
+        <v>146.095785</v>
       </c>
       <c r="N76">
-        <v>-100.6478412</v>
+        <v>-102.595785</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-100.6478412</v>
+        <v>-102.595785</v>
       </c>
       <c r="Q76">
-        <v>-82.64784119999999</v>
+        <v>-84.59578500000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.217931186547599</v>
+        <v>0.2248164340095029</v>
       </c>
       <c r="T76">
-        <v>3.355157213421742</v>
+        <v>3.489363501958612</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3017735100149388</v>
+        <v>0.2977498632147395</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2330541085023757</v>
+        <v>0.2349541085023757</v>
       </c>
       <c r="C77">
-        <v>-253.0357121995388</v>
+        <v>-262.8339489485742</v>
       </c>
       <c r="D77">
-        <v>153.0392878004613</v>
+        <v>151.5020510514259</v>
       </c>
       <c r="E77">
-        <v>511.1750000000001</v>
+        <v>519.436</v>
       </c>
       <c r="F77">
-        <v>619.575</v>
+        <v>627.836</v>
       </c>
       <c r="G77">
         <v>213.5</v>
@@ -7589,28 +7589,28 @@
         <v>43.5</v>
       </c>
       <c r="M77">
-        <v>146.095785</v>
+        <v>148.0437288</v>
       </c>
       <c r="N77">
-        <v>-102.595785</v>
+        <v>-104.5437288</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-102.595785</v>
+        <v>-104.5437288</v>
       </c>
       <c r="Q77">
-        <v>-84.59578500000001</v>
+        <v>-86.5437288</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2248164340095029</v>
+        <v>0.2322754520932322</v>
       </c>
       <c r="T77">
-        <v>3.489363501958612</v>
+        <v>3.634753647873554</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2977498632147395</v>
+        <v>0.2938321018566509</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2349541085023757</v>
+        <v>0.2368541085023757</v>
       </c>
       <c r="C78">
-        <v>-262.8339489485742</v>
+        <v>-272.6016105914674</v>
       </c>
       <c r="D78">
-        <v>151.5020510514259</v>
+        <v>149.9953894085326</v>
       </c>
       <c r="E78">
-        <v>519.436</v>
+        <v>527.697</v>
       </c>
       <c r="F78">
-        <v>627.836</v>
+        <v>636.097</v>
       </c>
       <c r="G78">
         <v>213.5</v>
@@ -7671,28 +7671,28 @@
         <v>43.5</v>
       </c>
       <c r="M78">
-        <v>148.0437288</v>
+        <v>149.9916726</v>
       </c>
       <c r="N78">
-        <v>-104.5437288</v>
+        <v>-106.4916726</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-104.5437288</v>
+        <v>-106.4916726</v>
       </c>
       <c r="Q78">
-        <v>-86.5437288</v>
+        <v>-88.49167260000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2322754520932322</v>
+        <v>0.2403830804451119</v>
       </c>
       <c r="T78">
-        <v>3.634753647873554</v>
+        <v>3.792786415172404</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2938321018566509</v>
+        <v>0.2900161005338372</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2368541085023757</v>
+        <v>0.2387541085023757</v>
       </c>
       <c r="C79">
-        <v>-272.6016105914674</v>
+        <v>-282.3396003383466</v>
       </c>
       <c r="D79">
-        <v>149.9953894085326</v>
+        <v>148.5183996616535</v>
       </c>
       <c r="E79">
-        <v>527.697</v>
+        <v>535.9580000000001</v>
       </c>
       <c r="F79">
-        <v>636.097</v>
+        <v>644.3580000000001</v>
       </c>
       <c r="G79">
         <v>213.5</v>
@@ -7753,28 +7753,28 @@
         <v>43.5</v>
       </c>
       <c r="M79">
-        <v>149.9916726</v>
+        <v>151.9396164</v>
       </c>
       <c r="N79">
-        <v>-106.4916726</v>
+        <v>-108.4396164</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-106.4916726</v>
+        <v>-108.4396164</v>
       </c>
       <c r="Q79">
-        <v>-88.49167260000002</v>
+        <v>-90.43961640000003</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2403830804451119</v>
+        <v>0.2492277659198897</v>
       </c>
       <c r="T79">
-        <v>3.792786415172404</v>
+        <v>3.965185797680241</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2900161005338372</v>
+        <v>0.2862979453987879</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2387541085023757</v>
+        <v>0.2406541085023757</v>
       </c>
       <c r="C80">
-        <v>-282.3396003383466</v>
+        <v>-292.0487861709471</v>
       </c>
       <c r="D80">
-        <v>148.5183996616535</v>
+        <v>147.0702138290529</v>
       </c>
       <c r="E80">
-        <v>535.9580000000001</v>
+        <v>544.2190000000001</v>
       </c>
       <c r="F80">
-        <v>644.3580000000001</v>
+        <v>652.619</v>
       </c>
       <c r="G80">
         <v>213.5</v>
@@ -7835,28 +7835,28 @@
         <v>43.5</v>
       </c>
       <c r="M80">
-        <v>151.9396164</v>
+        <v>153.8875602</v>
       </c>
       <c r="N80">
-        <v>-108.4396164</v>
+        <v>-110.3875602</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-108.4396164</v>
+        <v>-110.3875602</v>
       </c>
       <c r="Q80">
-        <v>-90.43961640000003</v>
+        <v>-92.38756020000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2492277659198897</v>
+        <v>0.2589148023922654</v>
       </c>
       <c r="T80">
-        <v>3.965185797680241</v>
+        <v>4.154004168998348</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2862979453987879</v>
+        <v>0.2826739207734869</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2406541085023757</v>
+        <v>0.2425541085023757</v>
       </c>
       <c r="C81">
-        <v>-292.0487861709471</v>
+        <v>-301.7300025435665</v>
       </c>
       <c r="D81">
-        <v>147.0702138290529</v>
+        <v>145.6499974564336</v>
       </c>
       <c r="E81">
-        <v>544.2190000000001</v>
+        <v>552.4800000000001</v>
       </c>
       <c r="F81">
-        <v>652.619</v>
+        <v>660.8800000000001</v>
       </c>
       <c r="G81">
         <v>213.5</v>
@@ -7917,28 +7917,28 @@
         <v>43.5</v>
       </c>
       <c r="M81">
-        <v>153.8875602</v>
+        <v>155.835504</v>
       </c>
       <c r="N81">
-        <v>-110.3875602</v>
+        <v>-112.335504</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-110.3875602</v>
+        <v>-112.335504</v>
       </c>
       <c r="Q81">
-        <v>-92.38756020000002</v>
+        <v>-94.33550400000004</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2589148023922654</v>
+        <v>0.2695705425118787</v>
       </c>
       <c r="T81">
-        <v>4.154004168998348</v>
+        <v>4.361704377448265</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2826739207734869</v>
+        <v>0.2791404967638182</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2425541085023757</v>
+        <v>0.2444541085023758</v>
       </c>
       <c r="C82">
-        <v>-301.7300025435665</v>
+        <v>-311.3840519864071</v>
       </c>
       <c r="D82">
-        <v>145.6499974564336</v>
+        <v>144.256948013593</v>
       </c>
       <c r="E82">
-        <v>552.4800000000001</v>
+        <v>560.7410000000001</v>
       </c>
       <c r="F82">
-        <v>660.8800000000001</v>
+        <v>669.1410000000001</v>
       </c>
       <c r="G82">
         <v>213.5</v>
@@ -7999,28 +7999,28 @@
         <v>43.5</v>
       </c>
       <c r="M82">
-        <v>155.835504</v>
+        <v>157.7834478</v>
       </c>
       <c r="N82">
-        <v>-112.335504</v>
+        <v>-114.2834478</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-112.335504</v>
+        <v>-114.2834478</v>
       </c>
       <c r="Q82">
-        <v>-94.33550400000004</v>
+        <v>-96.28344780000003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2695705425118787</v>
+        <v>0.2813479394861881</v>
       </c>
       <c r="T82">
-        <v>4.361704377448265</v>
+        <v>4.591267765735016</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2791404967638182</v>
+        <v>0.2756943177914255</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2444541085023758</v>
+        <v>0.2463541085023758</v>
       </c>
       <c r="C83">
-        <v>-311.3840519864071</v>
+        <v>-321.0117066177809</v>
       </c>
       <c r="D83">
-        <v>144.256948013593</v>
+        <v>142.8902933822191</v>
       </c>
       <c r="E83">
-        <v>560.7410000000001</v>
+        <v>569.0020000000001</v>
       </c>
       <c r="F83">
-        <v>669.1410000000001</v>
+        <v>677.402</v>
       </c>
       <c r="G83">
         <v>213.5</v>
@@ -8081,28 +8081,28 @@
         <v>43.5</v>
       </c>
       <c r="M83">
-        <v>157.7834478</v>
+        <v>159.7313916</v>
       </c>
       <c r="N83">
-        <v>-114.2834478</v>
+        <v>-116.2313916</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-114.2834478</v>
+        <v>-116.2313916</v>
       </c>
       <c r="Q83">
-        <v>-96.28344780000003</v>
+        <v>-98.23139160000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2813479394861881</v>
+        <v>0.2944339361243097</v>
       </c>
       <c r="T83">
-        <v>4.591267765735016</v>
+        <v>4.84633819716474</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2756943177914255</v>
+        <v>0.2723321919647008</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2463541085023758</v>
+        <v>0.2482541085023758</v>
       </c>
       <c r="C84">
-        <v>-321.0117066177809</v>
+        <v>-330.613709571164</v>
       </c>
       <c r="D84">
-        <v>142.8902933822191</v>
+        <v>141.5492904288361</v>
       </c>
       <c r="E84">
-        <v>569.0020000000001</v>
+        <v>577.2630000000001</v>
       </c>
       <c r="F84">
-        <v>677.402</v>
+        <v>685.6630000000001</v>
       </c>
       <c r="G84">
         <v>213.5</v>
@@ -8163,28 +8163,28 @@
         <v>43.5</v>
       </c>
       <c r="M84">
-        <v>159.7313916</v>
+        <v>161.6793354</v>
       </c>
       <c r="N84">
-        <v>-116.2313916</v>
+        <v>-118.1793354</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-116.2313916</v>
+        <v>-118.1793354</v>
       </c>
       <c r="Q84">
-        <v>-98.23139160000002</v>
+        <v>-100.1793354</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2944339361243097</v>
+        <v>0.3090594617786809</v>
       </c>
       <c r="T84">
-        <v>4.84633819716474</v>
+        <v>5.131416914645019</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2723321919647008</v>
+        <v>0.2690510812181381</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2482541085023758</v>
+        <v>0.2501541085023757</v>
       </c>
       <c r="C85">
-        <v>-330.613709571164</v>
+        <v>-340.190776342641</v>
       </c>
       <c r="D85">
-        <v>141.5492904288361</v>
+        <v>140.2332236573591</v>
       </c>
       <c r="E85">
-        <v>577.2630000000001</v>
+        <v>585.5240000000001</v>
       </c>
       <c r="F85">
-        <v>685.6630000000001</v>
+        <v>693.9240000000001</v>
       </c>
       <c r="G85">
         <v>213.5</v>
@@ -8245,28 +8245,28 @@
         <v>43.5</v>
       </c>
       <c r="M85">
-        <v>161.6793354</v>
+        <v>163.6272792</v>
       </c>
       <c r="N85">
-        <v>-118.1793354</v>
+        <v>-120.1272792</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-118.1793354</v>
+        <v>-120.1272792</v>
       </c>
       <c r="Q85">
-        <v>-100.1793354</v>
+        <v>-102.1272792</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3090594617786809</v>
+        <v>0.3255131781398484</v>
       </c>
       <c r="T85">
-        <v>5.131416914645019</v>
+        <v>5.452130471810333</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2690510812181381</v>
+        <v>0.2658480921560175</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2501541085023757</v>
+        <v>0.2520541085023758</v>
       </c>
       <c r="C86">
-        <v>-340.1907763426409</v>
+        <v>-349.7435960638753</v>
       </c>
       <c r="D86">
-        <v>140.2332236573591</v>
+        <v>138.9414039361247</v>
       </c>
       <c r="E86">
-        <v>585.524</v>
+        <v>593.785</v>
       </c>
       <c r="F86">
-        <v>693.924</v>
+        <v>702.1849999999999</v>
       </c>
       <c r="G86">
         <v>213.5</v>
@@ -8327,28 +8327,28 @@
         <v>43.5</v>
       </c>
       <c r="M86">
-        <v>163.6272792</v>
+        <v>165.575223</v>
       </c>
       <c r="N86">
-        <v>-120.1272792</v>
+        <v>-122.075223</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-120.1272792</v>
+        <v>-122.075223</v>
       </c>
       <c r="Q86">
-        <v>-102.1272792</v>
+        <v>-104.075223</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3255131781398483</v>
+        <v>0.3441607233491715</v>
       </c>
       <c r="T86">
-        <v>5.45213047181033</v>
+        <v>5.815605836597685</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2658480921560175</v>
+        <v>0.2627204675424173</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2520541085023758</v>
+        <v>0.2539541085023757</v>
       </c>
       <c r="C87">
-        <v>-349.7435960638753</v>
+        <v>-359.2728327053616</v>
       </c>
       <c r="D87">
-        <v>138.9414039361247</v>
+        <v>137.6731672946384</v>
       </c>
       <c r="E87">
-        <v>593.785</v>
+        <v>602.046</v>
       </c>
       <c r="F87">
-        <v>702.1849999999999</v>
+        <v>710.446</v>
       </c>
       <c r="G87">
         <v>213.5</v>
@@ -8409,28 +8409,28 @@
         <v>43.5</v>
       </c>
       <c r="M87">
-        <v>165.575223</v>
+        <v>167.5231668</v>
       </c>
       <c r="N87">
-        <v>-122.075223</v>
+        <v>-124.0231668</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-122.075223</v>
+        <v>-124.0231668</v>
       </c>
       <c r="Q87">
-        <v>-104.075223</v>
+        <v>-106.0231668</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3441607233491715</v>
+        <v>0.365472203588398</v>
       </c>
       <c r="T87">
-        <v>5.815605836597685</v>
+        <v>6.231006253497521</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2627204675424173</v>
+        <v>0.2596655783849473</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2539541085023757</v>
+        <v>0.2558541085023757</v>
       </c>
       <c r="C88">
-        <v>-359.2728327053616</v>
+        <v>-368.779126214376</v>
       </c>
       <c r="D88">
-        <v>137.6731672946384</v>
+        <v>136.427873785624</v>
       </c>
       <c r="E88">
-        <v>602.046</v>
+        <v>610.307</v>
       </c>
       <c r="F88">
-        <v>710.446</v>
+        <v>718.707</v>
       </c>
       <c r="G88">
         <v>213.5</v>
@@ -8491,28 +8491,28 @@
         <v>43.5</v>
       </c>
       <c r="M88">
-        <v>167.5231668</v>
+        <v>169.4711106</v>
       </c>
       <c r="N88">
-        <v>-124.0231668</v>
+        <v>-125.9711106</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-124.0231668</v>
+        <v>-125.9711106</v>
       </c>
       <c r="Q88">
-        <v>-106.0231668</v>
+        <v>-107.9711106</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.365472203588398</v>
+        <v>0.3900623730951979</v>
       </c>
       <c r="T88">
-        <v>6.231006253497521</v>
+        <v>6.710314426843484</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2596655783849473</v>
+        <v>0.2566809165644307</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2558541085023757</v>
+        <v>0.2577541085023757</v>
       </c>
       <c r="C89">
-        <v>-368.779126214376</v>
+        <v>-378.2630935917213</v>
       </c>
       <c r="D89">
-        <v>136.427873785624</v>
+        <v>135.2049064082788</v>
       </c>
       <c r="E89">
-        <v>610.307</v>
+        <v>618.5680000000001</v>
       </c>
       <c r="F89">
-        <v>718.707</v>
+        <v>726.9680000000001</v>
       </c>
       <c r="G89">
         <v>213.5</v>
@@ -8573,28 +8573,28 @@
         <v>43.5</v>
       </c>
       <c r="M89">
-        <v>169.4711106</v>
+        <v>171.4190544</v>
       </c>
       <c r="N89">
-        <v>-125.9711106</v>
+        <v>-127.9190544</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-125.9711106</v>
+        <v>-127.9190544</v>
       </c>
       <c r="Q89">
-        <v>-107.9711106</v>
+        <v>-109.9190544</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3900623730951979</v>
+        <v>0.4187509041864644</v>
       </c>
       <c r="T89">
-        <v>6.710314426843484</v>
+        <v>7.269507295747108</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2566809165644307</v>
+        <v>0.2537640879671076</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2577541085023757</v>
+        <v>0.2596541085023757</v>
       </c>
       <c r="C90">
-        <v>-378.2630935917213</v>
+        <v>-387.7253299110734</v>
       </c>
       <c r="D90">
-        <v>135.2049064082788</v>
+        <v>134.0036700889266</v>
       </c>
       <c r="E90">
-        <v>618.5680000000001</v>
+        <v>626.8290000000001</v>
       </c>
       <c r="F90">
-        <v>726.9680000000001</v>
+        <v>735.229</v>
       </c>
       <c r="G90">
         <v>213.5</v>
@@ -8655,28 +8655,28 @@
         <v>43.5</v>
       </c>
       <c r="M90">
-        <v>171.4190544</v>
+        <v>173.3669982</v>
       </c>
       <c r="N90">
-        <v>-127.9190544</v>
+        <v>-129.8669982</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-127.9190544</v>
+        <v>-129.8669982</v>
       </c>
       <c r="Q90">
-        <v>-109.9190544</v>
+        <v>-111.8669982</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4187509041864644</v>
+        <v>0.4526555318397794</v>
       </c>
       <c r="T90">
-        <v>7.269507295747108</v>
+        <v>7.930371595360482</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2537640879671076</v>
+        <v>0.2509128060798367</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2596541085023757</v>
+        <v>0.2615541085023758</v>
       </c>
       <c r="C91">
-        <v>-387.7253299110734</v>
+        <v>-397.1664092844688</v>
       </c>
       <c r="D91">
-        <v>134.0036700889266</v>
+        <v>132.8235907155312</v>
       </c>
       <c r="E91">
-        <v>626.8290000000001</v>
+        <v>635.09</v>
       </c>
       <c r="F91">
-        <v>735.229</v>
+        <v>743.49</v>
       </c>
       <c r="G91">
         <v>213.5</v>
@@ -8737,28 +8737,28 @@
         <v>43.5</v>
       </c>
       <c r="M91">
-        <v>173.3669982</v>
+        <v>175.314942</v>
       </c>
       <c r="N91">
-        <v>-129.8669982</v>
+        <v>-131.814942</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-129.8669982</v>
+        <v>-131.814942</v>
       </c>
       <c r="Q91">
-        <v>-111.8669982</v>
+        <v>-113.814942</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4526555318397794</v>
+        <v>0.4933410850237573</v>
       </c>
       <c r="T91">
-        <v>7.930371595360482</v>
+        <v>8.72340875489653</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2509128060798367</v>
+        <v>0.248124886012283</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2615541085023758</v>
+        <v>0.2634541085023757</v>
       </c>
       <c r="C92">
-        <v>-397.1664092844688</v>
+        <v>-406.5868857772213</v>
       </c>
       <c r="D92">
-        <v>132.8235907155312</v>
+        <v>131.6641142227788</v>
       </c>
       <c r="E92">
-        <v>635.09</v>
+        <v>643.3510000000001</v>
       </c>
       <c r="F92">
-        <v>743.49</v>
+        <v>751.7510000000001</v>
       </c>
       <c r="G92">
         <v>213.5</v>
@@ -8819,28 +8819,28 @@
         <v>43.5</v>
       </c>
       <c r="M92">
-        <v>175.314942</v>
+        <v>177.2628858</v>
       </c>
       <c r="N92">
-        <v>-131.814942</v>
+        <v>-133.7628858</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-131.814942</v>
+        <v>-133.7628858</v>
       </c>
       <c r="Q92">
-        <v>-113.814942</v>
+        <v>-115.7628858</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4933410850237573</v>
+        <v>0.5430678722486193</v>
       </c>
       <c r="T92">
-        <v>8.72340875489653</v>
+        <v>9.69267639432948</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.248124886012283</v>
+        <v>0.2453982389132469</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2634541085023757</v>
+        <v>0.2653541085023757</v>
       </c>
       <c r="C93">
-        <v>-406.5868857772213</v>
+        <v>-415.9872942753345</v>
       </c>
       <c r="D93">
-        <v>131.6641142227788</v>
+        <v>130.5247057246655</v>
       </c>
       <c r="E93">
-        <v>643.3510000000001</v>
+        <v>651.6120000000001</v>
       </c>
       <c r="F93">
-        <v>751.7510000000001</v>
+        <v>760.0120000000001</v>
       </c>
       <c r="G93">
         <v>213.5</v>
@@ -8901,28 +8901,28 @@
         <v>43.5</v>
       </c>
       <c r="M93">
-        <v>177.2628858</v>
+        <v>179.2108296</v>
       </c>
       <c r="N93">
-        <v>-133.7628858</v>
+        <v>-135.7108296</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-133.7628858</v>
+        <v>-135.7108296</v>
       </c>
       <c r="Q93">
-        <v>-115.7628858</v>
+        <v>-117.7108296</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5430678722486193</v>
+        <v>0.6052263562796968</v>
       </c>
       <c r="T93">
-        <v>9.69267639432948</v>
+        <v>10.90426094362067</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2453982389132469</v>
+        <v>0.2427308667511464</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2653541085023757</v>
+        <v>0.2672541085023757</v>
       </c>
       <c r="C94">
-        <v>-415.9872942753345</v>
+        <v>-425.368151308261</v>
       </c>
       <c r="D94">
-        <v>130.5247057246655</v>
+        <v>129.404848691739</v>
       </c>
       <c r="E94">
-        <v>651.6120000000001</v>
+        <v>659.873</v>
       </c>
       <c r="F94">
-        <v>760.0120000000001</v>
+        <v>768.273</v>
       </c>
       <c r="G94">
         <v>213.5</v>
@@ -8983,28 +8983,28 @@
         <v>43.5</v>
       </c>
       <c r="M94">
-        <v>179.2108296</v>
+        <v>181.1587734</v>
       </c>
       <c r="N94">
-        <v>-135.7108296</v>
+        <v>-137.6587734</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-135.7108296</v>
+        <v>-137.6587734</v>
       </c>
       <c r="Q94">
-        <v>-117.7108296</v>
+        <v>-119.6587734</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6052263562796968</v>
+        <v>0.6851444071767965</v>
       </c>
       <c r="T94">
-        <v>10.90426094362067</v>
+        <v>12.46201250699505</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2427308667511464</v>
+        <v>0.2401208574312416</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2672541085023757</v>
+        <v>0.2691541085023758</v>
       </c>
       <c r="C95">
-        <v>-425.368151308261</v>
+        <v>-434.7299558296684</v>
       </c>
       <c r="D95">
-        <v>129.404848691739</v>
+        <v>128.3040441703317</v>
       </c>
       <c r="E95">
-        <v>659.873</v>
+        <v>668.1340000000001</v>
       </c>
       <c r="F95">
-        <v>768.273</v>
+        <v>776.5340000000001</v>
       </c>
       <c r="G95">
         <v>213.5</v>
@@ -9065,28 +9065,28 @@
         <v>43.5</v>
       </c>
       <c r="M95">
-        <v>181.1587734</v>
+        <v>183.1067172</v>
       </c>
       <c r="N95">
-        <v>-137.6587734</v>
+        <v>-139.6067172</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-137.6587734</v>
+        <v>-139.6067172</v>
       </c>
       <c r="Q95">
-        <v>-119.6587734</v>
+        <v>-121.6067172</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6851444071767965</v>
+        <v>0.7917018083729294</v>
       </c>
       <c r="T95">
-        <v>12.46201250699505</v>
+        <v>14.53901459149423</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2401208574312416</v>
+        <v>0.2375663802245263</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2691541085023758</v>
+        <v>0.2710541085023758</v>
       </c>
       <c r="C96">
-        <v>-434.7299558296684</v>
+        <v>-444.0731899586901</v>
       </c>
       <c r="D96">
-        <v>128.3040441703317</v>
+        <v>127.22181004131</v>
       </c>
       <c r="E96">
-        <v>668.1340000000001</v>
+        <v>676.3950000000001</v>
       </c>
       <c r="F96">
-        <v>776.5340000000001</v>
+        <v>784.7950000000001</v>
       </c>
       <c r="G96">
         <v>213.5</v>
@@ -9147,28 +9147,28 @@
         <v>43.5</v>
       </c>
       <c r="M96">
-        <v>183.1067172</v>
+        <v>185.054661</v>
       </c>
       <c r="N96">
-        <v>-139.6067172</v>
+        <v>-141.554661</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-139.6067172</v>
+        <v>-141.554661</v>
       </c>
       <c r="Q96">
-        <v>-121.6067172</v>
+        <v>-123.554661</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7917018083729294</v>
+        <v>0.9408821700475157</v>
       </c>
       <c r="T96">
-        <v>14.53901459149423</v>
+        <v>17.44681750979308</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2375663802245263</v>
+        <v>0.2350656814853207</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2710541085023758</v>
+        <v>0.2729541085023757</v>
       </c>
       <c r="C97">
-        <v>-444.0731899586901</v>
+        <v>-453.3983196839772</v>
       </c>
       <c r="D97">
-        <v>127.22181004131</v>
+        <v>126.1576803160229</v>
       </c>
       <c r="E97">
-        <v>676.3950000000001</v>
+        <v>684.6560000000001</v>
       </c>
       <c r="F97">
-        <v>784.7950000000001</v>
+        <v>793.056</v>
       </c>
       <c r="G97">
         <v>213.5</v>
@@ -9229,28 +9229,28 @@
         <v>43.5</v>
       </c>
       <c r="M97">
-        <v>185.054661</v>
+        <v>187.0026048</v>
       </c>
       <c r="N97">
-        <v>-141.554661</v>
+        <v>-143.5026048</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-141.554661</v>
+        <v>-143.5026048</v>
       </c>
       <c r="Q97">
-        <v>-123.554661</v>
+        <v>-125.5026048</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9408821700475157</v>
+        <v>1.164652712559395</v>
       </c>
       <c r="T97">
-        <v>17.44681750979308</v>
+        <v>21.80852188724136</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2350656814853207</v>
+        <v>0.2326170806365152</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2729541085023758</v>
+        <v>0.2748541085023757</v>
       </c>
       <c r="C98">
-        <v>-453.3983196839773</v>
+        <v>-462.7057955327086</v>
       </c>
       <c r="D98">
-        <v>126.1576803160228</v>
+        <v>125.1112044672914</v>
       </c>
       <c r="E98">
-        <v>684.6560000000001</v>
+        <v>692.917</v>
       </c>
       <c r="F98">
-        <v>793.056</v>
+        <v>801.317</v>
       </c>
       <c r="G98">
         <v>213.5</v>
@@ -9311,28 +9311,28 @@
         <v>43.5</v>
       </c>
       <c r="M98">
-        <v>187.0026048</v>
+        <v>188.9505486</v>
       </c>
       <c r="N98">
-        <v>-143.5026048</v>
+        <v>-145.4505486</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-143.5026048</v>
+        <v>-145.4505486</v>
       </c>
       <c r="Q98">
-        <v>-125.5026048</v>
+        <v>-127.4505486</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.164652712559392</v>
+        <v>1.537603616745856</v>
       </c>
       <c r="T98">
-        <v>21.80852188724131</v>
+        <v>29.07802918298841</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2326170806365152</v>
+        <v>0.2302189664031491</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2748541085023757</v>
+        <v>0.2767541085023758</v>
       </c>
       <c r="C99">
-        <v>-462.7057955327086</v>
+        <v>-471.9960532065785</v>
       </c>
       <c r="D99">
-        <v>125.1112044672914</v>
+        <v>124.0819467934215</v>
       </c>
       <c r="E99">
-        <v>692.917</v>
+        <v>701.178</v>
       </c>
       <c r="F99">
-        <v>801.317</v>
+        <v>809.578</v>
       </c>
       <c r="G99">
         <v>213.5</v>
@@ -9393,28 +9393,28 @@
         <v>43.5</v>
       </c>
       <c r="M99">
-        <v>188.9505486</v>
+        <v>190.8984924</v>
       </c>
       <c r="N99">
-        <v>-145.4505486</v>
+        <v>-147.3984924</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-145.4505486</v>
+        <v>-147.3984924</v>
       </c>
       <c r="Q99">
-        <v>-127.4505486</v>
+        <v>-129.3984924</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.537603616745856</v>
+        <v>2.283505425118785</v>
       </c>
       <c r="T99">
-        <v>29.07802918298841</v>
+        <v>43.61704377448261</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2302189664031491</v>
+        <v>0.2278697932765864</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2767541085023758</v>
+        <v>0.2786541085023758</v>
       </c>
       <c r="C100">
-        <v>-471.9960532065785</v>
+        <v>-481.2695141866479</v>
       </c>
       <c r="D100">
-        <v>124.0819467934215</v>
+        <v>123.0694858133521</v>
       </c>
       <c r="E100">
-        <v>701.178</v>
+        <v>709.4390000000001</v>
       </c>
       <c r="F100">
-        <v>809.578</v>
+        <v>817.8390000000001</v>
       </c>
       <c r="G100">
         <v>213.5</v>
@@ -9475,28 +9475,28 @@
         <v>43.5</v>
       </c>
       <c r="M100">
-        <v>190.8984924</v>
+        <v>192.8464362</v>
       </c>
       <c r="N100">
-        <v>-147.3984924</v>
+        <v>-149.3464362</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-147.3984924</v>
+        <v>-149.3464362</v>
       </c>
       <c r="Q100">
-        <v>-129.3984924</v>
+        <v>-131.3464362</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.283505425118785</v>
+        <v>4.521210850237569</v>
       </c>
       <c r="T100">
-        <v>43.61704377448261</v>
+        <v>87.23408754896522</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2278697932765864</v>
+        <v>0.2255680781929845</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2786541085023758</v>
-      </c>
-      <c r="C101">
-        <v>-481.2695141866479</v>
-      </c>
-      <c r="D101">
-        <v>123.0694858133521</v>
-      </c>
-      <c r="E101">
-        <v>709.4390000000001</v>
-      </c>
-      <c r="F101">
-        <v>817.8390000000001</v>
-      </c>
-      <c r="G101">
-        <v>213.5</v>
-      </c>
-      <c r="H101">
-        <v>717.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>61.5</v>
-      </c>
-      <c r="K101">
-        <v>18</v>
-      </c>
-      <c r="L101">
-        <v>43.5</v>
-      </c>
-      <c r="M101">
-        <v>192.8464362</v>
-      </c>
-      <c r="N101">
-        <v>-149.3464362</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-149.3464362</v>
-      </c>
-      <c r="Q101">
-        <v>-131.3464362</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.521210850237569</v>
-      </c>
-      <c r="T101">
-        <v>87.23408754896522</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2255680781929845</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
